--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No contract" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ask the client'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By pack'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ask the client'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By pack'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Screens'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'No contract'!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,18 +494,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="56" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="56" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -541,15 +542,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>First release (POS, Guest App, White Labelling)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Who answers</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Answered on</t>
         </is>
@@ -586,13 +592,18 @@
           <t>Face Pass, facial readers, fingerprint enrolment</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yes: Face Pass enrolment is on the guest mobile app</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Client counsel</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -625,13 +636,18 @@
           <t>Every tenant storefront</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Yes: the guest web storefront</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -664,13 +680,18 @@
           <t>Finance, POS receipts, refunds</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Yes: POS receipts and refunds</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Client finance</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -703,13 +724,18 @@
           <t>The whole schedule</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Yes: the order everything is built in</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Client + us</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -744,11 +770,16 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>Client + us</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -781,13 +812,18 @@
           <t>Guest profiles, PII, the knowledge base</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Yes: guest profiles and account deletion on the guest apps</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -822,11 +858,16 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>Later: back-office dashboards</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t>Client + us</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -861,11 +902,16 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
+          <t>Later: none of the five screens is in the first release</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -890,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 28% of the API surface and they are exactly the operations with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 27% of the 2113 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -898,13 +944,18 @@
           <t>Back office: P08, P09, P10, P12, P13</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes, 1 of them: setReaderScannerPeripheral</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Client + us</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -937,13 +988,18 @@
           <t>P08 (124), P04 (1), P16 (1)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Yes, 1: setReaderScannerPeripheral</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -978,11 +1034,16 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
       <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1017,11 +1078,16 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1056,11 +1122,16 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1095,11 +1166,16 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1134,11 +1210,16 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1173,11 +1254,16 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1212,11 +1298,16 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1251,11 +1342,16 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1290,11 +1386,16 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1329,11 +1430,16 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1368,11 +1474,16 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
       <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1407,11 +1518,16 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1446,11 +1562,16 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1485,11 +1606,16 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1524,11 +1650,16 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1563,11 +1694,16 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1602,11 +1738,16 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1641,11 +1782,16 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1680,11 +1826,16 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1719,11 +1870,16 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
           <t>Client (confirm only)</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1756,13 +1912,18 @@
           <t>The whole schema</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Yes: every table</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Client backend</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1795,16 +1956,21 @@
           <t>Tenancy, everything below it</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Yes: every table</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Client backend</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1815,7 +1981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1825,6 +1991,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1863,6 +2030,11 @@
           <t>Platforms</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>In the first release</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1894,6 +2066,9 @@
           <t>P08 (124), P04 (1), P16 (1)</t>
         </is>
       </c>
+      <c r="H2" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1925,6 +2100,7 @@
           <t>P09 (114), P08 (8), P16 (1)</t>
         </is>
       </c>
+      <c r="H3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1956,6 +2132,7 @@
           <t>P09 (73), P08 (14)</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1987,6 +2164,7 @@
           <t>P10 (33), P09 (1), P17 (1)</t>
         </is>
       </c>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2018,6 +2196,7 @@
           <t>P08 (38)</t>
         </is>
       </c>
+      <c r="H6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2049,6 +2228,7 @@
           <t>P09 (38)</t>
         </is>
       </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2080,6 +2260,7 @@
           <t>P08 (31), P09 (3)</t>
         </is>
       </c>
+      <c r="H8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2111,6 +2292,7 @@
           <t>P13 (20), P08 (15), P09 (1)</t>
         </is>
       </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2142,6 +2324,7 @@
           <t>P08 (22), P09 (5)</t>
         </is>
       </c>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2173,6 +2356,7 @@
           <t>P09 (40), P08 (8)</t>
         </is>
       </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2204,6 +2388,7 @@
           <t>P09 (26), P17 (1)</t>
         </is>
       </c>
+      <c r="H12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2235,6 +2420,7 @@
           <t>P08 (23)</t>
         </is>
       </c>
+      <c r="H13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2266,6 +2452,7 @@
           <t>P13 (21), P08 (6)</t>
         </is>
       </c>
+      <c r="H14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2297,6 +2484,7 @@
           <t>P12 (21), P08 (18)</t>
         </is>
       </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2328,6 +2516,7 @@
           <t>P09 (23), P08 (1)</t>
         </is>
       </c>
+      <c r="H16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2359,6 +2548,7 @@
           <t>P09 (10), P08 (5)</t>
         </is>
       </c>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2390,9 +2580,10 @@
           <t>P09 (10)</t>
         </is>
       </c>
+      <c r="H18" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2403,7 +2594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I578"/>
+  <dimension ref="A1:J578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2414,7 +2605,8 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2460,6 +2652,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>In the first release</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Answer</t>
         </is>
       </c>
@@ -2499,7 +2696,8 @@
           <t>listAccess</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2536,7 +2734,8 @@
           <t>listVenueParkAccess</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2573,7 +2772,8 @@
           <t>setAccessAreaZone</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2610,7 +2810,8 @@
           <t>setAttractionAccess</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2647,7 +2848,8 @@
           <t>setGateLane</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2684,7 +2886,8 @@
           <t>setAccessGraphicalMap</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2721,7 +2924,8 @@
           <t>listAccessLocationGrouping</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2758,7 +2962,8 @@
           <t>listOperatingCalendarSpecial</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2795,7 +3000,8 @@
           <t>publishTopologyValidation</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2832,7 +3038,8 @@
           <t>listAccessRule</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2869,7 +3076,8 @@
           <t>setVisualAccessRule</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2906,7 +3114,8 @@
           <t>listEntryExitRule</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2943,7 +3152,8 @@
           <t>listAntiPassbackJourney</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2980,7 +3190,8 @@
           <t>listAccessValidityTime</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3017,7 +3228,8 @@
           <t>listEntitlementConsumption</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -3054,7 +3266,8 @@
           <t>listMultiParkCrossover</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3091,7 +3304,8 @@
           <t>listGuestCompanionEligibility</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -3128,7 +3342,8 @@
           <t>listGroupAdmissionQuantity</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3165,7 +3380,8 @@
           <t>publishRuleConflictCheck</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -3202,7 +3418,8 @@
           <t>listDigitalCredentialSecurity</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -3239,7 +3456,8 @@
           <t>setDynamicSecurityProfile</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3276,7 +3494,8 @@
           <t>listCredentialActivationDisplay</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3313,7 +3532,8 @@
           <t>listDeviceBindingSession</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -3350,7 +3570,8 @@
           <t>setBleBeaconGeofence</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3387,7 +3608,8 @@
           <t>listCredentialTransferRebinding</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3424,7 +3646,8 @@
           <t>listCredentialRevocationLifecycle</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3461,7 +3684,8 @@
           <t>listOfflineCryptographicValidation</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3498,7 +3722,8 @@
           <t>setEmbeddedEntitlementPayload</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -3535,7 +3760,8 @@
           <t>listCredentialSecurity</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3572,7 +3798,8 @@
           <t>listMediaCredential</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -3609,7 +3836,8 @@
           <t>listMediaTypeTechnology</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3646,7 +3874,8 @@
           <t>listVirtualCredentialMedia</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -3683,7 +3912,8 @@
           <t>listVerificationMethodSelection</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3720,7 +3950,8 @@
           <t>listMediaIssuanceEncoding</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -3757,7 +3988,8 @@
           <t>listMediaSwapReplacement</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3794,7 +4026,8 @@
           <t>setRfidNfc</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -3831,7 +4064,8 @@
           <t>listExternalPartnerCredential</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -3868,7 +4102,8 @@
           <t>listHotelWalletExternal</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -3905,7 +4140,8 @@
           <t>publishMediaCompatibilityTesting</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -3942,7 +4178,8 @@
           <t>listBiometricAccess</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3979,7 +4216,8 @@
           <t>setBiometricVerificationProfile</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -4016,7 +4254,8 @@
           <t>setFacePassEnrollment</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -4053,7 +4292,8 @@
           <t>listBiometricConsentGuardian</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -4090,7 +4330,8 @@
           <t>listFaceTagTemporary</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -4127,7 +4368,8 @@
           <t>listFaceMatchingVerification</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -4164,7 +4406,8 @@
           <t>listFaceChangeEnrollment</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -4201,7 +4444,8 @@
           <t>listBiometricValidationGate</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -4238,7 +4482,8 @@
           <t>listBiometricLifecycleRetention</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -4275,7 +4520,8 @@
           <t>listBiometric</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -4312,7 +4558,8 @@
           <t>listDeviceGate</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -4349,7 +4596,8 @@
           <t>listDeviceTypeHardware</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -4386,7 +4634,8 @@
           <t>listPhysicalDeviceRegistration</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -4423,7 +4672,8 @@
           <t>setTurnstileLaneBehavior</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -4460,7 +4710,8 @@
           <t>setValidationOutcomeGuest</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -4497,7 +4748,12 @@
           <t>setReaderScannerPeripheral</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -4534,7 +4790,8 @@
           <t>setHandheldMobileAccess</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -4571,7 +4828,8 @@
           <t>listGateModeFree</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -4608,7 +4866,8 @@
           <t>setDeviceSoftwareContent</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -4645,7 +4904,8 @@
           <t>listHardwareCompatibilityHealth</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -4682,7 +4942,8 @@
           <t>listOfflineEdge</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -4719,7 +4980,8 @@
           <t>setEdgeNodeLocal</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -4756,7 +5018,8 @@
           <t>listEdgePackageData</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4793,7 +5056,8 @@
           <t>listOfflineCredentialRevocation</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -4830,7 +5094,8 @@
           <t>listOfflineEntitlementUsage</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -4867,7 +5132,8 @@
           <t>listConnectivityFailureDegraded</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -4904,7 +5170,8 @@
           <t>listReconnectionSynchronizationConflict</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -4941,7 +5208,8 @@
           <t>simulateOfflineResilienceTesting</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -4978,7 +5246,8 @@
           <t>listEdgeSecurityDeployment</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -5015,7 +5284,8 @@
           <t>listGuestJourney</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -5052,7 +5322,8 @@
           <t>setGroupAdmissionProfile</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -5089,7 +5360,8 @@
           <t>listGroupLeaderFast</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -5126,7 +5398,8 @@
           <t>listGroupAttendancePartial</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -5163,7 +5436,8 @@
           <t>listFamilyChildPod</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -5200,7 +5474,8 @@
           <t>listEntryTemporaryExit</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -5237,7 +5512,8 @@
           <t>listMultiParkCrossover2</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -5274,7 +5550,8 @@
           <t>listFastPassAttraction</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -5311,7 +5588,8 @@
           <t>listSpecialEventFree</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -5348,7 +5626,8 @@
           <t>listLiveAccess</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -5385,7 +5664,8 @@
           <t>listPodiumConsole</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -5422,7 +5702,8 @@
           <t>listTicketCredentialInvestigation</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -5459,7 +5740,8 @@
           <t>listValidationExceptionReason</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -5496,7 +5778,8 @@
           <t>approveManualOverrideSupervisor</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -5533,7 +5816,8 @@
           <t>listCredentialDisableBlacklist</t>
         </is>
       </c>
-      <c r="I84" s="4" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -5570,7 +5854,8 @@
           <t>listLiveGateMode</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -5607,7 +5892,8 @@
           <t>listQueueThroughputLane</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -5644,7 +5930,8 @@
           <t>setOperationalIncidentException</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -5681,7 +5968,8 @@
           <t>listShiftHandoverSummary</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -5718,7 +6006,8 @@
           <t>listDynamicAccessPolicy</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -5755,7 +6044,8 @@
           <t>listAccessAttributeCatalog</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -5792,7 +6082,8 @@
           <t>setVisualDynamicPolicy</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -5829,7 +6120,8 @@
           <t>setContextTimeEvent</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -5866,7 +6158,8 @@
           <t>listIdentityMembershipAccreditation</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -5903,7 +6196,8 @@
           <t>listPolicyScopeHierarchy</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -5940,7 +6234,8 @@
           <t>listAuthorizationGovernanceTemporary</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -5977,7 +6272,8 @@
           <t>listPolicyEvaluationArchitecture</t>
         </is>
       </c>
-      <c r="I96" s="4" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -6014,7 +6310,8 @@
           <t>simulatePolicyConflictImpact</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -6051,7 +6348,8 @@
           <t>listAccessSecurityFraud</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -6088,7 +6386,8 @@
           <t>listFraudDetectionRule</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -6125,7 +6424,8 @@
           <t>listCredentialSharingConcurrent</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -6162,7 +6462,8 @@
           <t>listUnifiedIdentityCredential</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr"/>
+      <c r="I101" s="5" t="inlineStr"/>
+      <c r="J101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -6199,7 +6500,8 @@
           <t>listBiometricIdentityIntegrity</t>
         </is>
       </c>
-      <c r="I102" s="4" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -6236,7 +6538,8 @@
           <t>listRelationshipCompanionFraud</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr"/>
+      <c r="I103" s="5" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -6273,7 +6576,8 @@
           <t>listAccessRiskScoring</t>
         </is>
       </c>
-      <c r="I104" s="4" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -6310,7 +6614,8 @@
           <t>setRealTimeSecurity</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -6347,7 +6652,8 @@
           <t>setSecurityInvestigationEvidence</t>
         </is>
       </c>
-      <c r="I106" s="4" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -6384,7 +6690,8 @@
           <t>listSecurityDetectionGovernance</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr"/>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -6421,7 +6728,8 @@
           <t>listAccessMonitoring</t>
         </is>
       </c>
-      <c r="I108" s="4" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -6458,7 +6766,8 @@
           <t>listLiveVenueOccupancy</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr"/>
+      <c r="I109" s="5" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -6495,7 +6804,8 @@
           <t>listGraphicalAccessMap</t>
         </is>
       </c>
-      <c r="I110" s="4" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -6532,7 +6842,8 @@
           <t>listAttendanceAdmission</t>
         </is>
       </c>
-      <c r="I111" s="4" t="inlineStr"/>
+      <c r="I111" s="5" t="inlineStr"/>
+      <c r="J111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -6569,7 +6880,8 @@
           <t>listEntryExitCrossover</t>
         </is>
       </c>
-      <c r="I112" s="4" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -6606,7 +6918,8 @@
           <t>listThroughputQueueValidation</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr"/>
+      <c r="I113" s="5" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -6643,7 +6956,8 @@
           <t>listValidationOutcomeRejection</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -6680,7 +6994,8 @@
           <t>listGuestDwellTime</t>
         </is>
       </c>
-      <c r="I115" s="4" t="inlineStr"/>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -6717,7 +7032,8 @@
           <t>listAccessReportScheduled</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
@@ -6754,7 +7070,8 @@
           <t>listAccessExecutiveInsight</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -6791,7 +7108,8 @@
           <t>listPartner</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -6828,7 +7146,8 @@
           <t>setPartnerProfileOrganization</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr"/>
+      <c r="I119" s="5" t="inlineStr"/>
+      <c r="J119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -6865,7 +7184,8 @@
           <t>listPartnerOnboardingApplication</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -6902,7 +7222,8 @@
           <t>listPartnerContactUser</t>
         </is>
       </c>
-      <c r="I121" s="4" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -6939,7 +7260,8 @@
           <t>listTerritoryMarketDistribution</t>
         </is>
       </c>
-      <c r="I122" s="4" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -6976,7 +7298,8 @@
           <t>setPartnerBrandVenue</t>
         </is>
       </c>
-      <c r="I123" s="4" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr"/>
+      <c r="J123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -7013,7 +7336,8 @@
           <t>listPartnerDocumentationCompliance</t>
         </is>
       </c>
-      <c r="I124" s="4" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -7050,7 +7374,8 @@
           <t>listPartnerAccessRole</t>
         </is>
       </c>
-      <c r="I125" s="4" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -7087,7 +7412,8 @@
           <t>approvePartnerStatuLifecycle</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -7124,7 +7450,8 @@
           <t>listPartnerProfileReadiness</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -7161,7 +7488,8 @@
           <t>listCommercialAgreement</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -7198,7 +7526,8 @@
           <t>setAgreementContractTerm</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -7235,7 +7564,8 @@
           <t>setPartnerRateNet</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -7272,7 +7602,8 @@
           <t>listCommissionMarginIncentive</t>
         </is>
       </c>
-      <c r="I131" s="4" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -7309,7 +7640,8 @@
           <t>listCreditLimitExposure</t>
         </is>
       </c>
-      <c r="I132" s="4" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -7346,7 +7678,8 @@
           <t>listDepositGuaranteeFinancial</t>
         </is>
       </c>
-      <c r="I133" s="4" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr"/>
+      <c r="J133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -7383,7 +7716,8 @@
           <t>setPaymentTermBilling</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -7420,7 +7754,8 @@
           <t>listCommercialAllocationQuota</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr"/>
+      <c r="I135" s="5" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -7457,7 +7792,8 @@
           <t>approveBookingLimitCommercial</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -7494,7 +7830,8 @@
           <t>listCommercialAgreementHealth</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -7531,7 +7868,8 @@
           <t>listPartner2</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -7568,7 +7906,8 @@
           <t>listPartnerOrderBooking</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr"/>
+      <c r="J139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -7605,7 +7944,8 @@
           <t>listReservationHoldRelease</t>
         </is>
       </c>
-      <c r="I140" s="4" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -7642,7 +7982,8 @@
           <t>listPartnerCancellationRefund</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -7679,7 +8020,8 @@
           <t>listPartnerStatementAccount</t>
         </is>
       </c>
-      <c r="I142" s="4" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -7716,7 +8058,8 @@
           <t>listPartnerReconciliationException</t>
         </is>
       </c>
-      <c r="I143" s="4" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr"/>
+      <c r="J143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -7753,7 +8096,8 @@
           <t>listCommissionCalculationSettlement</t>
         </is>
       </c>
-      <c r="I144" s="4" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -7790,7 +8134,8 @@
           <t>listPartnerDisputeCase</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -7827,7 +8172,8 @@
           <t>listPartnerPerformanceScorecard</t>
         </is>
       </c>
-      <c r="I146" s="4" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -7864,7 +8210,8 @@
           <t>listPartnerRelationship</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr"/>
+      <c r="I147" s="5" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -7901,7 +8248,8 @@
           <t>listCommunicationService</t>
         </is>
       </c>
-      <c r="I148" s="4" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
@@ -7938,7 +8286,8 @@
           <t>setChannelProvider</t>
         </is>
       </c>
-      <c r="I149" s="4" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -7975,7 +8324,8 @@
           <t>setSenderIdentityDomain</t>
         </is>
       </c>
-      <c r="I150" s="4" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -8012,7 +8362,8 @@
           <t>listSystemTransactionalTemplate</t>
         </is>
       </c>
-      <c r="I151" s="4" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr"/>
+      <c r="J151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -8049,7 +8400,8 @@
           <t>listBusinessEventNotification</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -8086,7 +8438,8 @@
           <t>listRoutingPriorityThrottling</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr"/>
+      <c r="J153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -8123,7 +8476,8 @@
           <t>listConsentPreferenceCommunication</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -8160,7 +8514,8 @@
           <t>listDeliveryQueueFailure</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -8197,7 +8552,8 @@
           <t>listProviderHealthUsage</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
@@ -8234,7 +8590,8 @@
           <t>listDeliveryCommunicationPlatform</t>
         </is>
       </c>
-      <c r="I157" s="4" t="inlineStr"/>
+      <c r="I157" s="5" t="inlineStr"/>
+      <c r="J157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -8271,7 +8628,8 @@
           <t>listCustomerService</t>
         </is>
       </c>
-      <c r="I158" s="4" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -8308,7 +8666,8 @@
           <t>listCustomerServiceProfile</t>
         </is>
       </c>
-      <c r="I159" s="4" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr"/>
+      <c r="J159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -8345,7 +8704,8 @@
           <t>listUnifiedInteractionCommunication</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -8382,7 +8742,8 @@
           <t>createCaseClassificationIntelligent</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr"/>
+      <c r="I161" s="5" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -8419,7 +8780,8 @@
           <t>setCaseInvestigationResolution</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -8456,7 +8818,8 @@
           <t>setOrderBookingTicket</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr"/>
+      <c r="I163" s="5" t="inlineStr"/>
+      <c r="J163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -8493,7 +8856,8 @@
           <t>setRefundCompensationService</t>
         </is>
       </c>
-      <c r="I164" s="4" t="inlineStr"/>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -8530,7 +8894,8 @@
           <t>listEscalationCollaborationInternal</t>
         </is>
       </c>
-      <c r="I165" s="4" t="inlineStr"/>
+      <c r="I165" s="5" t="inlineStr"/>
+      <c r="J165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -8567,7 +8932,8 @@
           <t>listCaseResolutionClosure</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -8604,7 +8970,8 @@
           <t>setCustomerServiceCopilot</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr"/>
+      <c r="I167" s="5" t="inlineStr"/>
+      <c r="J167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -8641,7 +9008,8 @@
           <t>listContact</t>
         </is>
       </c>
-      <c r="I168" s="4" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -8678,7 +9046,8 @@
           <t>setIntelligentRoutingSkill</t>
         </is>
       </c>
-      <c r="I169" s="4" t="inlineStr"/>
+      <c r="I169" s="5" t="inlineStr"/>
+      <c r="J169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -8715,7 +9084,8 @@
           <t>listSlaPolicyService</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -8752,7 +9122,8 @@
           <t>listAgentWorkloadAvailability</t>
         </is>
       </c>
-      <c r="I171" s="4" t="inlineStr"/>
+      <c r="I171" s="5" t="inlineStr"/>
+      <c r="J171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -8789,7 +9160,8 @@
           <t>listEscalationCriticalCase</t>
         </is>
       </c>
-      <c r="I172" s="4" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -8826,7 +9198,8 @@
           <t>listQualityAgentEvaluation</t>
         </is>
       </c>
-      <c r="I173" s="4" t="inlineStr"/>
+      <c r="I173" s="5" t="inlineStr"/>
+      <c r="J173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -8863,7 +9236,8 @@
           <t>listCustomerSatisfactionFeedback</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -8900,7 +9274,8 @@
           <t>listServiceRootCause</t>
         </is>
       </c>
-      <c r="I175" s="4" t="inlineStr"/>
+      <c r="I175" s="5" t="inlineStr"/>
+      <c r="J175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -8937,7 +9312,8 @@
           <t>listContactAutomation</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -8974,7 +9350,8 @@
           <t>listGroupSale</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr"/>
+      <c r="I177" s="5" t="inlineStr"/>
+      <c r="J177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -9011,7 +9388,8 @@
           <t>listGroupEnquiryOpportunity</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -9048,7 +9426,8 @@
           <t>listGroupCustomerOrganization</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
+      <c r="I179" s="5" t="inlineStr"/>
+      <c r="J179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -9085,7 +9464,8 @@
           <t>listGroupRequirementAvailability</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -9122,7 +9502,8 @@
           <t>setGroupPackageExperience</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr"/>
+      <c r="I181" s="5" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -9159,7 +9540,8 @@
           <t>setGroupQuotationProposal</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -9196,7 +9578,8 @@
           <t>listQuoteRevisionNegotiation</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr"/>
+      <c r="I183" s="5" t="inlineStr"/>
+      <c r="J183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -9233,7 +9616,8 @@
           <t>approveGroupDiscountException</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -9270,7 +9654,8 @@
           <t>listQuoteBookingConversion</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr"/>
+      <c r="I185" s="5" t="inlineStr"/>
+      <c r="J185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -9307,7 +9692,8 @@
           <t>setGroupBookingHandover</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -9344,7 +9730,8 @@
           <t>listGroupBooking</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr"/>
+      <c r="I187" s="5" t="inlineStr"/>
+      <c r="J187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -9381,7 +9768,8 @@
           <t>setGroupOperationalPlanning</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -9418,7 +9806,8 @@
           <t>listParticipantGuestList</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr"/>
+      <c r="I189" s="5" t="inlineStr"/>
+      <c r="J189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -9455,7 +9844,8 @@
           <t>listGroupPaymentDeposit</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -9492,7 +9882,8 @@
           <t>listGroupTicketSeat</t>
         </is>
       </c>
-      <c r="I191" s="4" t="inlineStr"/>
+      <c r="I191" s="5" t="inlineStr"/>
+      <c r="J191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -9529,7 +9920,8 @@
           <t>listGroupTicketFulfillment</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr"/>
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
@@ -9566,7 +9958,8 @@
           <t>listGroupArrivalCheck</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr"/>
+      <c r="I193" s="5" t="inlineStr"/>
+      <c r="J193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -9603,7 +9996,8 @@
           <t>listGroupAmendmentCancellation</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -9640,7 +10034,8 @@
           <t>listGroupBookingReconciliation</t>
         </is>
       </c>
-      <c r="I195" s="4" t="inlineStr"/>
+      <c r="I195" s="5" t="inlineStr"/>
+      <c r="J195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -9677,7 +10072,8 @@
           <t>listGroupSale2</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -9714,7 +10110,8 @@
           <t>listMembershipAnnualPass</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr"/>
+      <c r="I197" s="5" t="inlineStr"/>
+      <c r="J197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -9751,7 +10148,8 @@
           <t>setMembershipProductTier</t>
         </is>
       </c>
-      <c r="I198" s="4" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -9788,7 +10186,8 @@
           <t>setMembershipEligibilityQualification</t>
         </is>
       </c>
-      <c r="I199" s="4" t="inlineStr"/>
+      <c r="I199" s="5" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -9825,7 +10224,8 @@
           <t>setValidityActivationExpiry</t>
         </is>
       </c>
-      <c r="I200" s="4" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
@@ -9862,7 +10262,8 @@
           <t>setMembershipEntitlementAdmission</t>
         </is>
       </c>
-      <c r="I201" s="4" t="inlineStr"/>
+      <c r="I201" s="5" t="inlineStr"/>
+      <c r="J201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -9899,7 +10300,8 @@
           <t>listMembershipUsageVisit</t>
         </is>
       </c>
-      <c r="I202" s="4" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -9936,7 +10338,8 @@
           <t>setFamilyHouseholdDependent</t>
         </is>
       </c>
-      <c r="I203" s="4" t="inlineStr"/>
+      <c r="I203" s="5" t="inlineStr"/>
+      <c r="J203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -9973,7 +10376,8 @@
           <t>listMembershipCommercialPricing</t>
         </is>
       </c>
-      <c r="I204" s="4" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -10010,7 +10414,8 @@
           <t>setRenewalAutoMembership</t>
         </is>
       </c>
-      <c r="I205" s="4" t="inlineStr"/>
+      <c r="I205" s="5" t="inlineStr"/>
+      <c r="J205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -10047,7 +10452,8 @@
           <t>approveMembershipProductValidation</t>
         </is>
       </c>
-      <c r="I206" s="4" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -10084,7 +10490,8 @@
           <t>listMember</t>
         </is>
       </c>
-      <c r="I207" s="4" t="inlineStr"/>
+      <c r="I207" s="5" t="inlineStr"/>
+      <c r="J207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -10121,7 +10528,8 @@
           <t>setMemberMembershipAccount</t>
         </is>
       </c>
-      <c r="I208" s="4" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -10158,7 +10566,8 @@
           <t>listMembershipActivationCredential</t>
         </is>
       </c>
-      <c r="I209" s="4" t="inlineStr"/>
+      <c r="I209" s="5" t="inlineStr"/>
+      <c r="J209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -10195,7 +10604,8 @@
           <t>listVisitAdmissionEntitlement</t>
         </is>
       </c>
-      <c r="I210" s="4" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -10232,7 +10642,8 @@
           <t>listMembershipFreezeSuspension</t>
         </is>
       </c>
-      <c r="I211" s="4" t="inlineStr"/>
+      <c r="I211" s="5" t="inlineStr"/>
+      <c r="J211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -10269,7 +10680,8 @@
           <t>listMembershipUpgradeDowngrade</t>
         </is>
       </c>
-      <c r="I212" s="4" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -10306,7 +10718,8 @@
           <t>listRenewalAuto</t>
         </is>
       </c>
-      <c r="I213" s="4" t="inlineStr"/>
+      <c r="I213" s="5" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -10343,7 +10756,8 @@
           <t>listMemberExceptionOverride</t>
         </is>
       </c>
-      <c r="I214" s="4" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
@@ -10380,7 +10794,8 @@
           <t>listMemberLifecycleCase</t>
         </is>
       </c>
-      <c r="I215" s="4" t="inlineStr"/>
+      <c r="I215" s="5" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -10417,7 +10832,8 @@
           <t>listMembershipRenewalRetention</t>
         </is>
       </c>
-      <c r="I216" s="4" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -10454,7 +10870,8 @@
           <t>listOrderReservation</t>
         </is>
       </c>
-      <c r="I217" s="4" t="inlineStr"/>
+      <c r="I217" s="5" t="inlineStr"/>
+      <c r="J217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -10491,7 +10908,8 @@
           <t>setOrderDetailTransaction</t>
         </is>
       </c>
-      <c r="I218" s="4" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -10528,7 +10946,8 @@
           <t>setReservationHoldPolicy</t>
         </is>
       </c>
-      <c r="I219" s="4" t="inlineStr"/>
+      <c r="I219" s="5" t="inlineStr"/>
+      <c r="J219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -10565,7 +10984,8 @@
           <t>setOrderReservationStatus</t>
         </is>
       </c>
-      <c r="I220" s="4" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -10602,7 +11022,8 @@
           <t>createOrderSourceChannel</t>
         </is>
       </c>
-      <c r="I221" s="4" t="inlineStr"/>
+      <c r="I221" s="5" t="inlineStr"/>
+      <c r="J221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -10639,7 +11060,8 @@
           <t>setCustomerGuestAccount</t>
         </is>
       </c>
-      <c r="I222" s="4" t="inlineStr"/>
+      <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -10676,7 +11098,8 @@
           <t>listOrderLineProduct</t>
         </is>
       </c>
-      <c r="I223" s="4" t="inlineStr"/>
+      <c r="I223" s="5" t="inlineStr"/>
+      <c r="J223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -10713,7 +11136,8 @@
           <t>listCapacityReservationInventory</t>
         </is>
       </c>
-      <c r="I224" s="4" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -10750,7 +11174,8 @@
           <t>listReservationConfirmationExpiry</t>
         </is>
       </c>
-      <c r="I225" s="4" t="inlineStr"/>
+      <c r="I225" s="5" t="inlineStr"/>
+      <c r="J225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -10787,7 +11212,8 @@
           <t>listOrderLifecycleTimeline</t>
         </is>
       </c>
-      <c r="I226" s="4" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -10824,7 +11250,8 @@
           <t>listAmendmentAfterSale</t>
         </is>
       </c>
-      <c r="I227" s="4" t="inlineStr"/>
+      <c r="I227" s="5" t="inlineStr"/>
+      <c r="J227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -10861,7 +11288,8 @@
           <t>setOrderAmendment</t>
         </is>
       </c>
-      <c r="I228" s="4" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
@@ -10898,7 +11326,8 @@
           <t>setAmendmentEligibilityPolicy</t>
         </is>
       </c>
-      <c r="I229" s="4" t="inlineStr"/>
+      <c r="I229" s="5" t="inlineStr"/>
+      <c r="J229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -10935,7 +11364,8 @@
           <t>setCancellationPartialPolicy</t>
         </is>
       </c>
-      <c r="I230" s="4" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -10972,7 +11402,8 @@
           <t>listVoidReversalSame</t>
         </is>
       </c>
-      <c r="I231" s="4" t="inlineStr"/>
+      <c r="I231" s="5" t="inlineStr"/>
+      <c r="J231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -11009,7 +11440,8 @@
           <t>listTicketReissueFulfillment</t>
         </is>
       </c>
-      <c r="I232" s="4" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -11046,7 +11478,8 @@
           <t>setAfterSaleFinancial</t>
         </is>
       </c>
-      <c r="I233" s="4" t="inlineStr"/>
+      <c r="I233" s="5" t="inlineStr"/>
+      <c r="J233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -11083,7 +11516,8 @@
           <t>approveExceptionServiceRecovery</t>
         </is>
       </c>
-      <c r="I234" s="4" t="inlineStr"/>
+      <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" s="4" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
@@ -11120,7 +11554,8 @@
           <t>listAmendmentAfterSale2</t>
         </is>
       </c>
-      <c r="I235" s="4" t="inlineStr"/>
+      <c r="I235" s="5" t="inlineStr"/>
+      <c r="J235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -11157,7 +11592,8 @@
           <t>listPaymentOrderFinancial</t>
         </is>
       </c>
-      <c r="I236" s="4" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
@@ -11194,7 +11630,8 @@
           <t>listOrderPaymentDetail</t>
         </is>
       </c>
-      <c r="I237" s="4" t="inlineStr"/>
+      <c r="I237" s="5" t="inlineStr"/>
+      <c r="J237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -11231,7 +11668,8 @@
           <t>setMultiPaymentSplit</t>
         </is>
       </c>
-      <c r="I238" s="4" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -11268,7 +11706,8 @@
           <t>listDepositPartialPayment</t>
         </is>
       </c>
-      <c r="I239" s="4" t="inlineStr"/>
+      <c r="I239" s="5" t="inlineStr"/>
+      <c r="J239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -11305,7 +11744,8 @@
           <t>listOrderSplitMerge</t>
         </is>
       </c>
-      <c r="I240" s="4" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr"/>
+      <c r="J240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
@@ -11342,7 +11782,8 @@
           <t>listRelatedOrderTransaction</t>
         </is>
       </c>
-      <c r="I241" s="4" t="inlineStr"/>
+      <c r="I241" s="5" t="inlineStr"/>
+      <c r="J241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -11379,7 +11820,8 @@
           <t>listExternalPaymentPartner</t>
         </is>
       </c>
-      <c r="I242" s="4" t="inlineStr"/>
+      <c r="I242" s="2" t="inlineStr"/>
+      <c r="J242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
@@ -11416,7 +11858,8 @@
           <t>listPaymentReconciliationException</t>
         </is>
       </c>
-      <c r="I243" s="4" t="inlineStr"/>
+      <c r="I243" s="5" t="inlineStr"/>
+      <c r="J243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -11453,7 +11896,8 @@
           <t>listFinancialTraceability</t>
         </is>
       </c>
-      <c r="I244" s="4" t="inlineStr"/>
+      <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -11490,7 +11934,8 @@
           <t>listOrderFinancialReconciliation</t>
         </is>
       </c>
-      <c r="I245" s="4" t="inlineStr"/>
+      <c r="I245" s="5" t="inlineStr"/>
+      <c r="J245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
@@ -11527,7 +11972,8 @@
           <t>listCommercialPricing</t>
         </is>
       </c>
-      <c r="I246" s="4" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr"/>
+      <c r="J246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -11564,7 +12010,8 @@
           <t>setPriceListMaster</t>
         </is>
       </c>
-      <c r="I247" s="4" t="inlineStr"/>
+      <c r="I247" s="5" t="inlineStr"/>
+      <c r="J247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -11601,7 +12048,8 @@
           <t>listPriceCategoryRate</t>
         </is>
       </c>
-      <c r="I248" s="4" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr"/>
+      <c r="J248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
@@ -11638,7 +12086,8 @@
           <t>setRateStructure</t>
         </is>
       </c>
-      <c r="I249" s="4" t="inlineStr"/>
+      <c r="I249" s="5" t="inlineStr"/>
+      <c r="J249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -11675,7 +12124,8 @@
           <t>setProductServicePrice</t>
         </is>
       </c>
-      <c r="I250" s="4" t="inlineStr"/>
+      <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
@@ -11712,7 +12162,8 @@
           <t>listPackageBundleAdd</t>
         </is>
       </c>
-      <c r="I251" s="4" t="inlineStr"/>
+      <c r="I251" s="5" t="inlineStr"/>
+      <c r="J251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -11749,7 +12200,8 @@
           <t>listMarketVenueCurrency</t>
         </is>
       </c>
-      <c r="I252" s="4" t="inlineStr"/>
+      <c r="I252" s="2" t="inlineStr"/>
+      <c r="J252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -11786,7 +12238,8 @@
           <t>setPriceHierarchyInheritance</t>
         </is>
       </c>
-      <c r="I253" s="4" t="inlineStr"/>
+      <c r="I253" s="5" t="inlineStr"/>
+      <c r="J253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -11823,7 +12276,8 @@
           <t>listPriceListTemplate</t>
         </is>
       </c>
-      <c r="I254" s="4" t="inlineStr"/>
+      <c r="I254" s="2" t="inlineStr"/>
+      <c r="J254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -11860,7 +12314,8 @@
           <t>listCommercialPricingStructure</t>
         </is>
       </c>
-      <c r="I255" s="4" t="inlineStr"/>
+      <c r="I255" s="5" t="inlineStr"/>
+      <c r="J255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -11897,7 +12352,8 @@
           <t>listPricingRule</t>
         </is>
       </c>
-      <c r="I256" s="4" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr"/>
+      <c r="J256" s="4" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -11934,7 +12390,8 @@
           <t>listCustomerSegmentProfile</t>
         </is>
       </c>
-      <c r="I257" s="4" t="inlineStr"/>
+      <c r="I257" s="5" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -11971,7 +12428,8 @@
           <t>listMembershipLoyaltyPricing</t>
         </is>
       </c>
-      <c r="I258" s="4" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr"/>
+      <c r="J258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -12008,7 +12466,8 @@
           <t>listResidencyNationalityMarket</t>
         </is>
       </c>
-      <c r="I259" s="4" t="inlineStr"/>
+      <c r="I259" s="5" t="inlineStr"/>
+      <c r="J259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -12045,7 +12504,8 @@
           <t>listChannelBasedPricing</t>
         </is>
       </c>
-      <c r="I260" s="4" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
@@ -12082,7 +12542,8 @@
           <t>listLocationVenueEvent</t>
         </is>
       </c>
-      <c r="I261" s="4" t="inlineStr"/>
+      <c r="I261" s="5" t="inlineStr"/>
+      <c r="J261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -12119,7 +12580,8 @@
           <t>listQuantityGroupVolume</t>
         </is>
       </c>
-      <c r="I262" s="4" t="inlineStr"/>
+      <c r="I262" s="2" t="inlineStr"/>
+      <c r="J262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
@@ -12156,7 +12618,8 @@
           <t>listEffectiveDateSeason</t>
         </is>
       </c>
-      <c r="I263" s="4" t="inlineStr"/>
+      <c r="I263" s="5" t="inlineStr"/>
+      <c r="J263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -12193,7 +12656,8 @@
           <t>listTimeslotPerformanceTime</t>
         </is>
       </c>
-      <c r="I264" s="4" t="inlineStr"/>
+      <c r="I264" s="2" t="inlineStr"/>
+      <c r="J264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
@@ -12230,7 +12694,8 @@
           <t>listPricingRulePriority</t>
         </is>
       </c>
-      <c r="I265" s="4" t="inlineStr"/>
+      <c r="I265" s="5" t="inlineStr"/>
+      <c r="J265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -12267,7 +12732,8 @@
           <t>listTaxFeeCalculation</t>
         </is>
       </c>
-      <c r="I266" s="4" t="inlineStr"/>
+      <c r="I266" s="2" t="inlineStr"/>
+      <c r="J266" s="4" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
@@ -12304,7 +12770,8 @@
           <t>setTaxProfileJurisdiction</t>
         </is>
       </c>
-      <c r="I267" s="4" t="inlineStr"/>
+      <c r="I267" s="5" t="inlineStr"/>
+      <c r="J267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -12341,7 +12808,8 @@
           <t>setTaxRuleTreatment</t>
         </is>
       </c>
-      <c r="I268" s="4" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr"/>
+      <c r="J268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
@@ -12378,7 +12846,8 @@
           <t>listFeeSurcharge</t>
         </is>
       </c>
-      <c r="I269" s="4" t="inlineStr"/>
+      <c r="I269" s="5" t="inlineStr"/>
+      <c r="J269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -12415,7 +12884,8 @@
           <t>setFeeApplicabilityCharging</t>
         </is>
       </c>
-      <c r="I270" s="4" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr"/>
+      <c r="J270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
@@ -12452,7 +12922,8 @@
           <t>listFeeWaiverTax</t>
         </is>
       </c>
-      <c r="I271" s="4" t="inlineStr"/>
+      <c r="I271" s="5" t="inlineStr"/>
+      <c r="J271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -12489,7 +12960,8 @@
           <t>listPriceCalculationSequence</t>
         </is>
       </c>
-      <c r="I272" s="4" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr"/>
+      <c r="J272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
@@ -12526,7 +12998,8 @@
           <t>listCurrencyPrecisionRounding</t>
         </is>
       </c>
-      <c r="I273" s="4" t="inlineStr"/>
+      <c r="I273" s="5" t="inlineStr"/>
+      <c r="J273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -12563,7 +13036,8 @@
           <t>simulatePriceBreakdownCalculation</t>
         </is>
       </c>
-      <c r="I274" s="4" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr"/>
+      <c r="J274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
@@ -12600,7 +13074,8 @@
           <t>listCalculationValidationReconciliation</t>
         </is>
       </c>
-      <c r="I275" s="4" t="inlineStr"/>
+      <c r="I275" s="5" t="inlineStr"/>
+      <c r="J275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -12637,7 +13112,8 @@
           <t>listPricingGovernance</t>
         </is>
       </c>
-      <c r="I276" s="4" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr"/>
+      <c r="J276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
@@ -12674,7 +13150,8 @@
           <t>setPricingChangeRequest</t>
         </is>
       </c>
-      <c r="I277" s="4" t="inlineStr"/>
+      <c r="I277" s="5" t="inlineStr"/>
+      <c r="J277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -12711,7 +13188,8 @@
           <t>listBulkPricingUpdate</t>
         </is>
       </c>
-      <c r="I278" s="4" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr"/>
+      <c r="J278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
@@ -12748,7 +13226,8 @@
           <t>listPricingVersionBaseline</t>
         </is>
       </c>
-      <c r="I279" s="4" t="inlineStr"/>
+      <c r="I279" s="5" t="inlineStr"/>
+      <c r="J279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -12785,7 +13264,8 @@
           <t>listPricingChangeImpact</t>
         </is>
       </c>
-      <c r="I280" s="4" t="inlineStr"/>
+      <c r="I280" s="2" t="inlineStr"/>
+      <c r="J280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -12822,7 +13302,8 @@
           <t>approvePricingWorkflowAuthority</t>
         </is>
       </c>
-      <c r="I281" s="4" t="inlineStr"/>
+      <c r="I281" s="5" t="inlineStr"/>
+      <c r="J281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -12859,7 +13340,8 @@
           <t>publishPricingEffectiveDate</t>
         </is>
       </c>
-      <c r="I282" s="4" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr"/>
+      <c r="J282" s="4" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
@@ -12896,7 +13378,8 @@
           <t>listPricingDistributionSynchronization</t>
         </is>
       </c>
-      <c r="I283" s="4" t="inlineStr"/>
+      <c r="I283" s="5" t="inlineStr"/>
+      <c r="J283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -12933,7 +13416,8 @@
           <t>listPricingRollbackEmergency</t>
         </is>
       </c>
-      <c r="I284" s="4" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
@@ -12970,7 +13454,8 @@
           <t>listPricingCompliance</t>
         </is>
       </c>
-      <c r="I285" s="4" t="inlineStr"/>
+      <c r="I285" s="5" t="inlineStr"/>
+      <c r="J285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -13007,7 +13492,8 @@
           <t>listDynamicPricingStrategy</t>
         </is>
       </c>
-      <c r="I286" s="4" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr"/>
+      <c r="J286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
@@ -13044,7 +13530,8 @@
           <t>setDynamicPricingStrategy</t>
         </is>
       </c>
-      <c r="I287" s="4" t="inlineStr"/>
+      <c r="I287" s="5" t="inlineStr"/>
+      <c r="J287" s="4" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -13081,7 +13568,8 @@
           <t>setDemandOccupancyAvailability</t>
         </is>
       </c>
-      <c r="I288" s="4" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" s="4" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
@@ -13118,7 +13606,8 @@
           <t>setBookingVelocityTime</t>
         </is>
       </c>
-      <c r="I289" s="4" t="inlineStr"/>
+      <c r="I289" s="5" t="inlineStr"/>
+      <c r="J289" s="4" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -13155,7 +13644,8 @@
           <t>listSeasonalCalendarDay</t>
         </is>
       </c>
-      <c r="I290" s="4" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr"/>
+      <c r="J290" s="4" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
@@ -13192,7 +13682,8 @@
           <t>listChannelCustomerSegment</t>
         </is>
       </c>
-      <c r="I291" s="4" t="inlineStr"/>
+      <c r="I291" s="5" t="inlineStr"/>
+      <c r="J291" s="4" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -13229,7 +13720,8 @@
           <t>listDynamicPriceBand</t>
         </is>
       </c>
-      <c r="I292" s="4" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr"/>
+      <c r="J292" s="4" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
@@ -13266,7 +13758,8 @@
           <t>listDynamicPricingGuardrail</t>
         </is>
       </c>
-      <c r="I293" s="4" t="inlineStr"/>
+      <c r="I293" s="5" t="inlineStr"/>
+      <c r="J293" s="4" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -13303,7 +13796,8 @@
           <t>listDynamicPricingAutomation</t>
         </is>
       </c>
-      <c r="I294" s="4" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr"/>
+      <c r="J294" s="4" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
@@ -13340,7 +13834,8 @@
           <t>listRulePriorityConflict</t>
         </is>
       </c>
-      <c r="I295" s="4" t="inlineStr"/>
+      <c r="I295" s="5" t="inlineStr"/>
+      <c r="J295" s="4" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -13377,7 +13872,8 @@
           <t>listPricing</t>
         </is>
       </c>
-      <c r="I296" s="4" t="inlineStr"/>
+      <c r="I296" s="2" t="inlineStr"/>
+      <c r="J296" s="4" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
@@ -13414,7 +13910,8 @@
           <t>listInternalDemandBooking</t>
         </is>
       </c>
-      <c r="I297" s="4" t="inlineStr"/>
+      <c r="I297" s="5" t="inlineStr"/>
+      <c r="J297" s="4" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -13451,7 +13948,8 @@
           <t>listWeatherDemandImpact</t>
         </is>
       </c>
-      <c r="I298" s="4" t="inlineStr"/>
+      <c r="I298" s="2" t="inlineStr"/>
+      <c r="J298" s="4" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
@@ -13488,7 +13986,8 @@
           <t>listNearbyEventExhibition</t>
         </is>
       </c>
-      <c r="I299" s="4" t="inlineStr"/>
+      <c r="I299" s="5" t="inlineStr"/>
+      <c r="J299" s="4" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -13525,7 +14024,8 @@
           <t>listCompetitorPricingMarket</t>
         </is>
       </c>
-      <c r="I300" s="4" t="inlineStr"/>
+      <c r="I300" s="2" t="inlineStr"/>
+      <c r="J300" s="4" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
@@ -13562,7 +14062,8 @@
           <t>listMarketTourismHoliday</t>
         </is>
       </c>
-      <c r="I301" s="4" t="inlineStr"/>
+      <c r="I301" s="5" t="inlineStr"/>
+      <c r="J301" s="4" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
@@ -13599,7 +14100,8 @@
           <t>listDemandBookingCurve</t>
         </is>
       </c>
-      <c r="I302" s="4" t="inlineStr"/>
+      <c r="I302" s="2" t="inlineStr"/>
+      <c r="J302" s="4" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
@@ -13636,7 +14138,8 @@
           <t>listPriceElasticityRevenue</t>
         </is>
       </c>
-      <c r="I303" s="4" t="inlineStr"/>
+      <c r="I303" s="5" t="inlineStr"/>
+      <c r="J303" s="4" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -13673,7 +14176,8 @@
           <t>listPricingRecommendationExplainability</t>
         </is>
       </c>
-      <c r="I304" s="4" t="inlineStr"/>
+      <c r="I304" s="2" t="inlineStr"/>
+      <c r="J304" s="4" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
@@ -13710,7 +14214,8 @@
           <t>listSignalDataQuality</t>
         </is>
       </c>
-      <c r="I305" s="4" t="inlineStr"/>
+      <c r="I305" s="5" t="inlineStr"/>
+      <c r="J305" s="4" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -13747,7 +14252,8 @@
           <t>listRevenue</t>
         </is>
       </c>
-      <c r="I306" s="4" t="inlineStr"/>
+      <c r="I306" s="2" t="inlineStr"/>
+      <c r="J306" s="4" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
@@ -13784,7 +14290,8 @@
           <t>setPricing</t>
         </is>
       </c>
-      <c r="I307" s="4" t="inlineStr"/>
+      <c r="I307" s="5" t="inlineStr"/>
+      <c r="J307" s="4" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -13821,7 +14328,8 @@
           <t>listScenarioModelingWhat</t>
         </is>
       </c>
-      <c r="I308" s="4" t="inlineStr"/>
+      <c r="I308" s="2" t="inlineStr"/>
+      <c r="J308" s="4" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
@@ -13858,7 +14366,8 @@
           <t>setPricingExperiment</t>
         </is>
       </c>
-      <c r="I309" s="4" t="inlineStr"/>
+      <c r="I309" s="5" t="inlineStr"/>
+      <c r="J309" s="4" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -13895,7 +14404,8 @@
           <t>listRevenueDemandImpact</t>
         </is>
       </c>
-      <c r="I310" s="4" t="inlineStr"/>
+      <c r="I310" s="2" t="inlineStr"/>
+      <c r="J310" s="4" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
@@ -13932,7 +14442,8 @@
           <t>listRecommendationReviewDecision</t>
         </is>
       </c>
-      <c r="I311" s="4" t="inlineStr"/>
+      <c r="I311" s="5" t="inlineStr"/>
+      <c r="J311" s="4" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
@@ -13969,7 +14480,8 @@
           <t>listAutomationPolicyAutonomous</t>
         </is>
       </c>
-      <c r="I312" s="4" t="inlineStr"/>
+      <c r="I312" s="2" t="inlineStr"/>
+      <c r="J312" s="4" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
@@ -14006,7 +14518,8 @@
           <t>createLiveDynamicPrice</t>
         </is>
       </c>
-      <c r="I313" s="4" t="inlineStr"/>
+      <c r="I313" s="5" t="inlineStr"/>
+      <c r="J313" s="4" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -14043,7 +14556,8 @@
           <t>listDynamicPricingPerformance</t>
         </is>
       </c>
-      <c r="I314" s="4" t="inlineStr"/>
+      <c r="I314" s="2" t="inlineStr"/>
+      <c r="J314" s="4" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
@@ -14080,7 +14594,8 @@
           <t>listLearningModelPerformance</t>
         </is>
       </c>
-      <c r="I315" s="4" t="inlineStr"/>
+      <c r="I315" s="5" t="inlineStr"/>
+      <c r="J315" s="4" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
@@ -14117,7 +14632,8 @@
           <t>listPrivacyConsent</t>
         </is>
       </c>
-      <c r="I316" s="4" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr"/>
+      <c r="J316" s="4" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
@@ -14154,7 +14670,8 @@
           <t>listDataProcessingPurpose</t>
         </is>
       </c>
-      <c r="I317" s="4" t="inlineStr"/>
+      <c r="I317" s="5" t="inlineStr"/>
+      <c r="J317" s="4" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
@@ -14191,7 +14708,8 @@
           <t>setCommunicationPreferenceMarketing</t>
         </is>
       </c>
-      <c r="I318" s="4" t="inlineStr"/>
+      <c r="I318" s="2" t="inlineStr"/>
+      <c r="J318" s="4" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
@@ -14228,7 +14746,8 @@
           <t>listCookieTrackingDigital</t>
         </is>
       </c>
-      <c r="I319" s="4" t="inlineStr"/>
+      <c r="I319" s="5" t="inlineStr"/>
+      <c r="J319" s="4" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -14265,7 +14784,8 @@
           <t>listCookieBannerPreference</t>
         </is>
       </c>
-      <c r="I320" s="4" t="inlineStr"/>
+      <c r="I320" s="2" t="inlineStr"/>
+      <c r="J320" s="4" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
@@ -14302,7 +14822,8 @@
           <t>setConsentCapturePoint</t>
         </is>
       </c>
-      <c r="I321" s="4" t="inlineStr"/>
+      <c r="I321" s="5" t="inlineStr"/>
+      <c r="J321" s="4" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
@@ -14339,7 +14860,8 @@
           <t>listPrivacyNoticePolicy</t>
         </is>
       </c>
-      <c r="I322" s="4" t="inlineStr"/>
+      <c r="I322" s="2" t="inlineStr"/>
+      <c r="J322" s="4" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
@@ -14376,7 +14898,8 @@
           <t>setMinorGuardianAge</t>
         </is>
       </c>
-      <c r="I323" s="4" t="inlineStr"/>
+      <c r="I323" s="5" t="inlineStr"/>
+      <c r="J323" s="4" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -14413,7 +14936,8 @@
           <t>approvePrivacyTesting</t>
         </is>
       </c>
-      <c r="I324" s="4" t="inlineStr"/>
+      <c r="I324" s="2" t="inlineStr"/>
+      <c r="J324" s="4" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
@@ -14450,7 +14974,8 @@
           <t>listPrivacy</t>
         </is>
       </c>
-      <c r="I325" s="4" t="inlineStr"/>
+      <c r="I325" s="5" t="inlineStr"/>
+      <c r="J325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -14487,7 +15012,8 @@
           <t>listCustomerPrivacyConsent</t>
         </is>
       </c>
-      <c r="I326" s="4" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr"/>
+      <c r="J326" s="4" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
@@ -14524,7 +15050,8 @@
           <t>listConsentEvidenceWithdrawal</t>
         </is>
       </c>
-      <c r="I327" s="4" t="inlineStr"/>
+      <c r="I327" s="5" t="inlineStr"/>
+      <c r="J327" s="4" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
@@ -14561,7 +15088,8 @@
           <t>listDataSubjectCustomer</t>
         </is>
       </c>
-      <c r="I328" s="4" t="inlineStr"/>
+      <c r="I328" s="2" t="inlineStr"/>
+      <c r="J328" s="4" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
@@ -14598,7 +15126,8 @@
           <t>setDataDiscoveryAccess</t>
         </is>
       </c>
-      <c r="I329" s="4" t="inlineStr"/>
+      <c r="I329" s="5" t="inlineStr"/>
+      <c r="J329" s="4" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
@@ -14635,7 +15164,8 @@
           <t>listDeletionAnonymizationRestriction</t>
         </is>
       </c>
-      <c r="I330" s="4" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr"/>
+      <c r="J330" s="4" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
@@ -14672,7 +15202,8 @@
           <t>listDataRetentionExpiry</t>
         </is>
       </c>
-      <c r="I331" s="4" t="inlineStr"/>
+      <c r="I331" s="5" t="inlineStr"/>
+      <c r="J331" s="4" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
@@ -14709,7 +15240,8 @@
           <t>setPrivacyComplianceException</t>
         </is>
       </c>
-      <c r="I332" s="4" t="inlineStr"/>
+      <c r="I332" s="2" t="inlineStr"/>
+      <c r="J332" s="4" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
@@ -14746,7 +15278,8 @@
           <t>listPrivacyEvidenceCompliance</t>
         </is>
       </c>
-      <c r="I333" s="4" t="inlineStr"/>
+      <c r="I333" s="5" t="inlineStr"/>
+      <c r="J333" s="4" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -14783,7 +15316,8 @@
           <t>listPrivacyCompliance</t>
         </is>
       </c>
-      <c r="I334" s="4" t="inlineStr"/>
+      <c r="I334" s="2" t="inlineStr"/>
+      <c r="J334" s="4" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
@@ -14820,7 +15354,8 @@
           <t>listProductLifecycle</t>
         </is>
       </c>
-      <c r="I335" s="4" t="inlineStr"/>
+      <c r="I335" s="5" t="inlineStr"/>
+      <c r="J335" s="4" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
@@ -14857,7 +15392,8 @@
           <t>setLifecycleStatuWorkflow</t>
         </is>
       </c>
-      <c r="I336" s="4" t="inlineStr"/>
+      <c r="I336" s="2" t="inlineStr"/>
+      <c r="J336" s="4" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
@@ -14894,7 +15430,8 @@
           <t>createBulkProductCatalogue</t>
         </is>
       </c>
-      <c r="I337" s="4" t="inlineStr"/>
+      <c r="I337" s="5" t="inlineStr"/>
+      <c r="J337" s="4" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -14931,7 +15468,8 @@
           <t>listProductImportExport</t>
         </is>
       </c>
-      <c r="I338" s="4" t="inlineStr"/>
+      <c r="I338" s="2" t="inlineStr"/>
+      <c r="J338" s="4" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
@@ -14968,7 +15506,8 @@
           <t>setProductContextOwnership</t>
         </is>
       </c>
-      <c r="I339" s="4" t="inlineStr"/>
+      <c r="I339" s="5" t="inlineStr"/>
+      <c r="J339" s="4" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -15005,7 +15544,8 @@
           <t>publishChannelAvailability</t>
         </is>
       </c>
-      <c r="I340" s="4" t="inlineStr"/>
+      <c r="I340" s="2" t="inlineStr"/>
+      <c r="J340" s="4" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
@@ -15042,7 +15582,8 @@
           <t>publishActivationScheduler</t>
         </is>
       </c>
-      <c r="I341" s="4" t="inlineStr"/>
+      <c r="I341" s="5" t="inlineStr"/>
+      <c r="J341" s="4" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -15079,7 +15620,8 @@
           <t>listProductDuplicationTemplate</t>
         </is>
       </c>
-      <c r="I342" s="4" t="inlineStr"/>
+      <c r="I342" s="2" t="inlineStr"/>
+      <c r="J342" s="4" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
@@ -15116,7 +15658,8 @@
           <t>setCatalogueReview</t>
         </is>
       </c>
-      <c r="I343" s="4" t="inlineStr"/>
+      <c r="I343" s="5" t="inlineStr"/>
+      <c r="J343" s="4" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
@@ -15153,7 +15696,8 @@
           <t>listProductGovernance</t>
         </is>
       </c>
-      <c r="I344" s="4" t="inlineStr"/>
+      <c r="I344" s="2" t="inlineStr"/>
+      <c r="J344" s="4" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
@@ -15190,7 +15734,8 @@
           <t>approveWorkflow</t>
         </is>
       </c>
-      <c r="I345" s="4" t="inlineStr"/>
+      <c r="I345" s="5" t="inlineStr"/>
+      <c r="J345" s="4" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
@@ -15227,7 +15772,8 @@
           <t>approveReviewDecision</t>
         </is>
       </c>
-      <c r="I346" s="4" t="inlineStr"/>
+      <c r="I346" s="2" t="inlineStr"/>
+      <c r="J346" s="4" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
@@ -15264,7 +15810,8 @@
           <t>listRollbackRecovery</t>
         </is>
       </c>
-      <c r="I347" s="4" t="inlineStr"/>
+      <c r="I347" s="5" t="inlineStr"/>
+      <c r="J347" s="4" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
@@ -15301,7 +15848,8 @@
           <t>listChangeImpactAnalysis</t>
         </is>
       </c>
-      <c r="I348" s="4" t="inlineStr"/>
+      <c r="I348" s="2" t="inlineStr"/>
+      <c r="J348" s="4" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
@@ -15338,7 +15886,8 @@
           <t>listChangePropagationDependency</t>
         </is>
       </c>
-      <c r="I349" s="4" t="inlineStr"/>
+      <c r="I349" s="5" t="inlineStr"/>
+      <c r="J349" s="4" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
@@ -15375,7 +15924,8 @@
           <t>listProductRetirementSuspension</t>
         </is>
       </c>
-      <c r="I350" s="4" t="inlineStr"/>
+      <c r="I350" s="2" t="inlineStr"/>
+      <c r="J350" s="4" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
@@ -15412,7 +15962,8 @@
           <t>listProductTrailChange</t>
         </is>
       </c>
-      <c r="I351" s="4" t="inlineStr"/>
+      <c r="I351" s="5" t="inlineStr"/>
+      <c r="J351" s="4" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -15449,7 +16000,8 @@
           <t>listGovernanceRiskMonitoring</t>
         </is>
       </c>
-      <c r="I352" s="4" t="inlineStr"/>
+      <c r="I352" s="2" t="inlineStr"/>
+      <c r="J352" s="4" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
@@ -15486,7 +16038,8 @@
           <t>listPromotionCampaign</t>
         </is>
       </c>
-      <c r="I353" s="4" t="inlineStr"/>
+      <c r="I353" s="5" t="inlineStr"/>
+      <c r="J353" s="4" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -15523,7 +16076,8 @@
           <t>listPromotionLifecycleStatus</t>
         </is>
       </c>
-      <c r="I354" s="4" t="inlineStr"/>
+      <c r="I354" s="2" t="inlineStr"/>
+      <c r="J354" s="4" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
@@ -15560,7 +16114,8 @@
           <t>listCampaignCalendarTimeline</t>
         </is>
       </c>
-      <c r="I355" s="4" t="inlineStr"/>
+      <c r="I355" s="5" t="inlineStr"/>
+      <c r="J355" s="4" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
@@ -15597,7 +16152,8 @@
           <t>listPromotionChannel</t>
         </is>
       </c>
-      <c r="I356" s="4" t="inlineStr"/>
+      <c r="I356" s="2" t="inlineStr"/>
+      <c r="J356" s="4" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
@@ -15634,7 +16190,8 @@
           <t>listPromotionAlertException</t>
         </is>
       </c>
-      <c r="I357" s="4" t="inlineStr"/>
+      <c r="I357" s="5" t="inlineStr"/>
+      <c r="J357" s="4" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
@@ -15671,7 +16228,8 @@
           <t>listPromotionHealthPerformance</t>
         </is>
       </c>
-      <c r="I358" s="4" t="inlineStr"/>
+      <c r="I358" s="2" t="inlineStr"/>
+      <c r="J358" s="4" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
@@ -15708,7 +16266,8 @@
           <t>listPromotionActivityVersion</t>
         </is>
       </c>
-      <c r="I359" s="4" t="inlineStr"/>
+      <c r="I359" s="5" t="inlineStr"/>
+      <c r="J359" s="4" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -15745,7 +16304,8 @@
           <t>setPromotionRule</t>
         </is>
       </c>
-      <c r="I360" s="4" t="inlineStr"/>
+      <c r="I360" s="2" t="inlineStr"/>
+      <c r="J360" s="4" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
@@ -15782,7 +16342,8 @@
           <t>listPercentageFixedDiscount</t>
         </is>
       </c>
-      <c r="I361" s="4" t="inlineStr"/>
+      <c r="I361" s="5" t="inlineStr"/>
+      <c r="J361" s="4" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -15819,7 +16380,8 @@
           <t>listCartTransactionThreshold</t>
         </is>
       </c>
-      <c r="I362" s="4" t="inlineStr"/>
+      <c r="I362" s="2" t="inlineStr"/>
+      <c r="J362" s="4" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
@@ -15856,7 +16418,8 @@
           <t>listVolumeBulkTier</t>
         </is>
       </c>
-      <c r="I363" s="4" t="inlineStr"/>
+      <c r="I363" s="5" t="inlineStr"/>
+      <c r="J363" s="4" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
@@ -15893,7 +16456,8 @@
           <t>listTimeBasedSeasonal</t>
         </is>
       </c>
-      <c r="I364" s="4" t="inlineStr"/>
+      <c r="I364" s="2" t="inlineStr"/>
+      <c r="J364" s="4" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
@@ -15930,7 +16494,8 @@
           <t>listCustomerMembershipSegment</t>
         </is>
       </c>
-      <c r="I365" s="4" t="inlineStr"/>
+      <c r="I365" s="5" t="inlineStr"/>
+      <c r="J365" s="4" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
@@ -15967,7 +16532,8 @@
           <t>listPaymentMethodBank</t>
         </is>
       </c>
-      <c r="I366" s="4" t="inlineStr"/>
+      <c r="I366" s="2" t="inlineStr"/>
+      <c r="J366" s="4" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
@@ -16004,7 +16570,8 @@
           <t>listSpecialPriceGuest</t>
         </is>
       </c>
-      <c r="I367" s="4" t="inlineStr"/>
+      <c r="I367" s="5" t="inlineStr"/>
+      <c r="J367" s="4" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
@@ -16041,7 +16608,8 @@
           <t>listDiscountLimitGuardrail</t>
         </is>
       </c>
-      <c r="I368" s="4" t="inlineStr"/>
+      <c r="I368" s="2" t="inlineStr"/>
+      <c r="J368" s="4" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
@@ -16078,7 +16646,8 @@
           <t>setRuleTestRecommendation</t>
         </is>
       </c>
-      <c r="I369" s="4" t="inlineStr"/>
+      <c r="I369" s="5" t="inlineStr"/>
+      <c r="J369" s="4" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
@@ -16115,7 +16684,8 @@
           <t>simulateBundlePreviewRecommendation</t>
         </is>
       </c>
-      <c r="I370" s="4" t="inlineStr"/>
+      <c r="I370" s="2" t="inlineStr"/>
+      <c r="J370" s="4" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
@@ -16152,7 +16722,8 @@
           <t>setCouponPromoCode</t>
         </is>
       </c>
-      <c r="I371" s="4" t="inlineStr"/>
+      <c r="I371" s="5" t="inlineStr"/>
+      <c r="J371" s="4" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
@@ -16189,7 +16760,8 @@
           <t>listUniqueCodeGeneration</t>
         </is>
       </c>
-      <c r="I372" s="4" t="inlineStr"/>
+      <c r="I372" s="2" t="inlineStr"/>
+      <c r="J372" s="4" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
@@ -16226,7 +16798,8 @@
           <t>listCodeEligibilityRestriction</t>
         </is>
       </c>
-      <c r="I373" s="4" t="inlineStr"/>
+      <c r="I373" s="5" t="inlineStr"/>
+      <c r="J373" s="4" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
@@ -16263,7 +16836,8 @@
           <t>listUsageCapacityFrequency</t>
         </is>
       </c>
-      <c r="I374" s="4" t="inlineStr"/>
+      <c r="I374" s="2" t="inlineStr"/>
+      <c r="J374" s="4" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
@@ -16300,7 +16874,8 @@
           <t>listValidityDateTime</t>
         </is>
       </c>
-      <c r="I375" s="4" t="inlineStr"/>
+      <c r="I375" s="5" t="inlineStr"/>
+      <c r="J375" s="4" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
@@ -16337,7 +16912,8 @@
           <t>setCodeDistributionManager</t>
         </is>
       </c>
-      <c r="I376" s="4" t="inlineStr"/>
+      <c r="I376" s="2" t="inlineStr"/>
+      <c r="J376" s="4" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
@@ -16374,7 +16950,8 @@
           <t>listRedemptionCodeLookup</t>
         </is>
       </c>
-      <c r="I377" s="4" t="inlineStr"/>
+      <c r="I377" s="5" t="inlineStr"/>
+      <c r="J377" s="4" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
@@ -16411,7 +16988,8 @@
           <t>listCodeSecurityFraud</t>
         </is>
       </c>
-      <c r="I378" s="4" t="inlineStr"/>
+      <c r="I378" s="2" t="inlineStr"/>
+      <c r="J378" s="4" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
@@ -16448,7 +17026,8 @@
           <t>listRedemption</t>
         </is>
       </c>
-      <c r="I379" s="4" t="inlineStr"/>
+      <c r="I379" s="5" t="inlineStr"/>
+      <c r="J379" s="4" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
@@ -16485,7 +17064,8 @@
           <t>listAdvancedOffer</t>
         </is>
       </c>
-      <c r="I380" s="4" t="inlineStr"/>
+      <c r="I380" s="2" t="inlineStr"/>
+      <c r="J380" s="4" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
@@ -16522,7 +17102,8 @@
           <t>setBuyGetBogo</t>
         </is>
       </c>
-      <c r="I381" s="4" t="inlineStr"/>
+      <c r="I381" s="5" t="inlineStr"/>
+      <c r="J381" s="4" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
@@ -16559,7 +17140,8 @@
           <t>listMultiBuyQuantity</t>
         </is>
       </c>
-      <c r="I382" s="4" t="inlineStr"/>
+      <c r="I382" s="2" t="inlineStr"/>
+      <c r="J382" s="4" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
@@ -16596,7 +17178,8 @@
           <t>listCheapestLowestValue</t>
         </is>
       </c>
-      <c r="I383" s="4" t="inlineStr"/>
+      <c r="I383" s="5" t="inlineStr"/>
+      <c r="J383" s="4" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
@@ -16633,7 +17216,8 @@
           <t>setFixedPriceOffer</t>
         </is>
       </c>
-      <c r="I384" s="4" t="inlineStr"/>
+      <c r="I384" s="2" t="inlineStr"/>
+      <c r="J384" s="4" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
@@ -16670,7 +17254,8 @@
           <t>setGiftFreeProduct</t>
         </is>
       </c>
-      <c r="I385" s="4" t="inlineStr"/>
+      <c r="I385" s="5" t="inlineStr"/>
+      <c r="J385" s="4" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
@@ -16707,7 +17292,8 @@
           <t>setCrossCategoryPromotion</t>
         </is>
       </c>
-      <c r="I386" s="4" t="inlineStr"/>
+      <c r="I386" s="2" t="inlineStr"/>
+      <c r="J386" s="4" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
@@ -16744,7 +17330,8 @@
           <t>listRewardSelectionSubstitution</t>
         </is>
       </c>
-      <c r="I387" s="4" t="inlineStr"/>
+      <c r="I387" s="5" t="inlineStr"/>
+      <c r="J387" s="4" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -16781,7 +17368,8 @@
           <t>listAdvancedOfferGuardrail</t>
         </is>
       </c>
-      <c r="I388" s="4" t="inlineStr"/>
+      <c r="I388" s="2" t="inlineStr"/>
+      <c r="J388" s="4" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
@@ -16818,7 +17406,8 @@
           <t>listOfferBasketTrace</t>
         </is>
       </c>
-      <c r="I389" s="4" t="inlineStr"/>
+      <c r="I389" s="5" t="inlineStr"/>
+      <c r="J389" s="4" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -16855,7 +17444,8 @@
           <t>listBundleCombo</t>
         </is>
       </c>
-      <c r="I390" s="4" t="inlineStr"/>
+      <c r="I390" s="2" t="inlineStr"/>
+      <c r="J390" s="4" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
@@ -16892,7 +17482,8 @@
           <t>setBundleDefinition</t>
         </is>
       </c>
-      <c r="I391" s="4" t="inlineStr"/>
+      <c r="I391" s="5" t="inlineStr"/>
+      <c r="J391" s="4" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
@@ -16929,7 +17520,8 @@
           <t>setBundleComponent</t>
         </is>
       </c>
-      <c r="I392" s="4" t="inlineStr"/>
+      <c r="I392" s="2" t="inlineStr"/>
+      <c r="J392" s="4" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
@@ -16966,7 +17558,8 @@
           <t>setGuestChoiceBuild</t>
         </is>
       </c>
-      <c r="I393" s="4" t="inlineStr"/>
+      <c r="I393" s="5" t="inlineStr"/>
+      <c r="J393" s="4" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
@@ -17003,7 +17596,8 @@
           <t>listBundlePricingCommercial</t>
         </is>
       </c>
-      <c r="I394" s="4" t="inlineStr"/>
+      <c r="I394" s="2" t="inlineStr"/>
+      <c r="J394" s="4" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
@@ -17040,7 +17634,8 @@
           <t>listBundleAvailabilityCapacity</t>
         </is>
       </c>
-      <c r="I395" s="4" t="inlineStr"/>
+      <c r="I395" s="5" t="inlineStr"/>
+      <c r="J395" s="4" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
@@ -17077,7 +17672,8 @@
           <t>listBundleValidityScheduling</t>
         </is>
       </c>
-      <c r="I396" s="4" t="inlineStr"/>
+      <c r="I396" s="2" t="inlineStr"/>
+      <c r="J396" s="4" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
@@ -17114,7 +17710,8 @@
           <t>listPartnerExternalProduct</t>
         </is>
       </c>
-      <c r="I397" s="4" t="inlineStr"/>
+      <c r="I397" s="5" t="inlineStr"/>
+      <c r="J397" s="4" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -17151,7 +17748,8 @@
           <t>listRevenueAllocationCost</t>
         </is>
       </c>
-      <c r="I398" s="4" t="inlineStr"/>
+      <c r="I398" s="2" t="inlineStr"/>
+      <c r="J398" s="4" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
@@ -17188,7 +17786,8 @@
           <t>listDynamicBundle</t>
         </is>
       </c>
-      <c r="I399" s="4" t="inlineStr"/>
+      <c r="I399" s="5" t="inlineStr"/>
+      <c r="J399" s="4" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
@@ -17225,7 +17824,8 @@
           <t>listComponentInventoryAvailability</t>
         </is>
       </c>
-      <c r="I400" s="4" t="inlineStr"/>
+      <c r="I400" s="2" t="inlineStr"/>
+      <c r="J400" s="4" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="6" t="inlineStr">
@@ -17262,7 +17862,8 @@
           <t>listBundleSellabilityDependency</t>
         </is>
       </c>
-      <c r="I401" s="4" t="inlineStr"/>
+      <c r="I401" s="5" t="inlineStr"/>
+      <c r="J401" s="4" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
@@ -17299,7 +17900,8 @@
           <t>listCapacityPoolReservation</t>
         </is>
       </c>
-      <c r="I402" s="4" t="inlineStr"/>
+      <c r="I402" s="2" t="inlineStr"/>
+      <c r="J402" s="4" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="6" t="inlineStr">
@@ -17336,7 +17938,8 @@
           <t>listDynamicComponentSubstitution</t>
         </is>
       </c>
-      <c r="I403" s="4" t="inlineStr"/>
+      <c r="I403" s="5" t="inlineStr"/>
+      <c r="J403" s="4" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
@@ -17373,7 +17976,8 @@
           <t>listDynamicBundleRule</t>
         </is>
       </c>
-      <c r="I404" s="4" t="inlineStr"/>
+      <c r="I404" s="2" t="inlineStr"/>
+      <c r="J404" s="4" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="6" t="inlineStr">
@@ -17410,7 +18014,8 @@
           <t>listRealTimeAvailability</t>
         </is>
       </c>
-      <c r="I405" s="4" t="inlineStr"/>
+      <c r="I405" s="5" t="inlineStr"/>
+      <c r="J405" s="4" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
@@ -17447,7 +18052,8 @@
           <t>listBundleAvailabilityChannel</t>
         </is>
       </c>
-      <c r="I406" s="4" t="inlineStr"/>
+      <c r="I406" s="2" t="inlineStr"/>
+      <c r="J406" s="4" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
@@ -17484,7 +18090,8 @@
           <t>listBundleAvailabilityForecast</t>
         </is>
       </c>
-      <c r="I407" s="4" t="inlineStr"/>
+      <c r="I407" s="5" t="inlineStr"/>
+      <c r="J407" s="4" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -17521,7 +18128,8 @@
           <t>listDynamicBundle2</t>
         </is>
       </c>
-      <c r="I408" s="4" t="inlineStr"/>
+      <c r="I408" s="2" t="inlineStr"/>
+      <c r="J408" s="4" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="6" t="inlineStr">
@@ -17558,7 +18166,8 @@
           <t>listTargetingEligibility</t>
         </is>
       </c>
-      <c r="I409" s="4" t="inlineStr"/>
+      <c r="I409" s="5" t="inlineStr"/>
+      <c r="J409" s="4" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -17595,7 +18204,8 @@
           <t>setEligibilityRule</t>
         </is>
       </c>
-      <c r="I410" s="4" t="inlineStr"/>
+      <c r="I410" s="2" t="inlineStr"/>
+      <c r="J410" s="4" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="6" t="inlineStr">
@@ -17632,7 +18242,8 @@
           <t>listCrmCustomerSegment</t>
         </is>
       </c>
-      <c r="I411" s="4" t="inlineStr"/>
+      <c r="I411" s="5" t="inlineStr"/>
+      <c r="J411" s="4" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -17669,7 +18280,8 @@
           <t>listMembershipLoyaltyGuest</t>
         </is>
       </c>
-      <c r="I412" s="4" t="inlineStr"/>
+      <c r="I412" s="2" t="inlineStr"/>
+      <c r="J412" s="4" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
@@ -17706,7 +18318,8 @@
           <t>listBehavioralTransactionTargeting</t>
         </is>
       </c>
-      <c r="I413" s="4" t="inlineStr"/>
+      <c r="I413" s="5" t="inlineStr"/>
+      <c r="J413" s="4" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
@@ -17743,7 +18356,8 @@
           <t>listContextLocationChannel</t>
         </is>
       </c>
-      <c r="I414" s="4" t="inlineStr"/>
+      <c r="I414" s="2" t="inlineStr"/>
+      <c r="J414" s="4" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="6" t="inlineStr">
@@ -17780,7 +18394,8 @@
           <t>listPartnerPaymentEligibility</t>
         </is>
       </c>
-      <c r="I415" s="4" t="inlineStr"/>
+      <c r="I415" s="5" t="inlineStr"/>
+      <c r="J415" s="4" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
@@ -17817,7 +18432,8 @@
           <t>listAudiencePreviewReach</t>
         </is>
       </c>
-      <c r="I416" s="4" t="inlineStr"/>
+      <c r="I416" s="2" t="inlineStr"/>
+      <c r="J416" s="4" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
@@ -17854,7 +18470,8 @@
           <t>listTargetingConflictFrequency</t>
         </is>
       </c>
-      <c r="I417" s="4" t="inlineStr"/>
+      <c r="I417" s="5" t="inlineStr"/>
+      <c r="J417" s="4" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -17891,7 +18508,8 @@
           <t>listAudienceDiscoveryTargeting</t>
         </is>
       </c>
-      <c r="I418" s="4" t="inlineStr"/>
+      <c r="I418" s="2" t="inlineStr"/>
+      <c r="J418" s="4" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="6" t="inlineStr">
@@ -17928,7 +18546,8 @@
           <t>listStackingConflict</t>
         </is>
       </c>
-      <c r="I419" s="4" t="inlineStr"/>
+      <c r="I419" s="5" t="inlineStr"/>
+      <c r="J419" s="4" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
@@ -17965,7 +18584,8 @@
           <t>listPromotionPriorityHierarchy</t>
         </is>
       </c>
-      <c r="I420" s="4" t="inlineStr"/>
+      <c r="I420" s="2" t="inlineStr"/>
+      <c r="J420" s="4" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
@@ -18002,7 +18622,8 @@
           <t>setPromotionStackingRule</t>
         </is>
       </c>
-      <c r="I421" s="4" t="inlineStr"/>
+      <c r="I421" s="5" t="inlineStr"/>
+      <c r="J421" s="4" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
@@ -18039,7 +18660,8 @@
           <t>listPromotionExclusionCompatibility</t>
         </is>
       </c>
-      <c r="I422" s="4" t="inlineStr"/>
+      <c r="I422" s="2" t="inlineStr"/>
+      <c r="J422" s="4" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="6" t="inlineStr">
@@ -18076,7 +18698,8 @@
           <t>listDiscountCalculationApplication</t>
         </is>
       </c>
-      <c r="I423" s="4" t="inlineStr"/>
+      <c r="I423" s="5" t="inlineStr"/>
+      <c r="J423" s="4" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
@@ -18113,7 +18736,8 @@
           <t>listBestOfferCustomer</t>
         </is>
       </c>
-      <c r="I424" s="4" t="inlineStr"/>
+      <c r="I424" s="2" t="inlineStr"/>
+      <c r="J424" s="4" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="6" t="inlineStr">
@@ -18150,7 +18774,8 @@
           <t>listDiscountCapMaximum</t>
         </is>
       </c>
-      <c r="I425" s="4" t="inlineStr"/>
+      <c r="I425" s="5" t="inlineStr"/>
+      <c r="J425" s="4" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -18187,7 +18812,8 @@
           <t>listConflictDetectionResolution</t>
         </is>
       </c>
-      <c r="I426" s="4" t="inlineStr"/>
+      <c r="I426" s="2" t="inlineStr"/>
+      <c r="J426" s="4" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
@@ -18224,7 +18850,8 @@
           <t>listPromotionDecisionTrace</t>
         </is>
       </c>
-      <c r="I427" s="4" t="inlineStr"/>
+      <c r="I427" s="5" t="inlineStr"/>
+      <c r="J427" s="4" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
@@ -18261,7 +18888,8 @@
           <t>listConflict</t>
         </is>
       </c>
-      <c r="I428" s="4" t="inlineStr"/>
+      <c r="I428" s="2" t="inlineStr"/>
+      <c r="J428" s="4" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
@@ -18298,7 +18926,8 @@
           <t>listCampaignGovernanceBudget</t>
         </is>
       </c>
-      <c r="I429" s="4" t="inlineStr"/>
+      <c r="I429" s="5" t="inlineStr"/>
+      <c r="J429" s="4" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -18335,7 +18964,8 @@
           <t>setCampaignBudgetFinancial</t>
         </is>
       </c>
-      <c r="I430" s="4" t="inlineStr"/>
+      <c r="I430" s="2" t="inlineStr"/>
+      <c r="J430" s="4" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="6" t="inlineStr">
@@ -18372,7 +19002,8 @@
           <t>listRedemptionDiscountExposure</t>
         </is>
       </c>
-      <c r="I431" s="4" t="inlineStr"/>
+      <c r="I431" s="5" t="inlineStr"/>
+      <c r="J431" s="4" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -18409,7 +19040,8 @@
           <t>listBudgetConsumptionForecast</t>
         </is>
       </c>
-      <c r="I432" s="4" t="inlineStr"/>
+      <c r="I432" s="2" t="inlineStr"/>
+      <c r="J432" s="4" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="6" t="inlineStr">
@@ -18446,7 +19078,8 @@
           <t>listThresholdActionAutomatic</t>
         </is>
       </c>
-      <c r="I433" s="4" t="inlineStr"/>
+      <c r="I433" s="5" t="inlineStr"/>
+      <c r="J433" s="4" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
@@ -18483,7 +19116,8 @@
           <t>approveCampaignWorkflow</t>
         </is>
       </c>
-      <c r="I434" s="4" t="inlineStr"/>
+      <c r="I434" s="2" t="inlineStr"/>
+      <c r="J434" s="4" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
@@ -18520,7 +19154,8 @@
           <t>approveDecision</t>
         </is>
       </c>
-      <c r="I435" s="4" t="inlineStr"/>
+      <c r="I435" s="5" t="inlineStr"/>
+      <c r="J435" s="4" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -18557,7 +19192,8 @@
           <t>listCampaignFinancialCommercial</t>
         </is>
       </c>
-      <c r="I436" s="4" t="inlineStr"/>
+      <c r="I436" s="2" t="inlineStr"/>
+      <c r="J436" s="4" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="6" t="inlineStr">
@@ -18594,7 +19230,8 @@
           <t>listCampaignExperimentTest</t>
         </is>
       </c>
-      <c r="I437" s="4" t="inlineStr"/>
+      <c r="I437" s="5" t="inlineStr"/>
+      <c r="J437" s="4" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
@@ -18631,7 +19268,8 @@
           <t>listGovernanceRiskLaunch</t>
         </is>
       </c>
-      <c r="I438" s="4" t="inlineStr"/>
+      <c r="I438" s="2" t="inlineStr"/>
+      <c r="J438" s="4" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="6" t="inlineStr">
@@ -18668,7 +19306,8 @@
           <t>listPromotionPerformance</t>
         </is>
       </c>
-      <c r="I439" s="4" t="inlineStr"/>
+      <c r="I439" s="5" t="inlineStr"/>
+      <c r="J439" s="4" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -18705,7 +19344,8 @@
           <t>listCampaignPromotionPerformance</t>
         </is>
       </c>
-      <c r="I440" s="4" t="inlineStr"/>
+      <c r="I440" s="2" t="inlineStr"/>
+      <c r="J440" s="4" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
@@ -18742,7 +19382,8 @@
           <t>listRedemptionConversionFunnel</t>
         </is>
       </c>
-      <c r="I441" s="4" t="inlineStr"/>
+      <c r="I441" s="5" t="inlineStr"/>
+      <c r="J441" s="4" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
@@ -18779,7 +19420,8 @@
           <t>listDiscountMarginProfitability</t>
         </is>
       </c>
-      <c r="I442" s="4" t="inlineStr"/>
+      <c r="I442" s="2" t="inlineStr"/>
+      <c r="J442" s="4" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="6" t="inlineStr">
@@ -18816,7 +19458,8 @@
           <t>listBundleBogoAdvanced</t>
         </is>
       </c>
-      <c r="I443" s="4" t="inlineStr"/>
+      <c r="I443" s="5" t="inlineStr"/>
+      <c r="J443" s="4" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -18853,7 +19496,8 @@
           <t>listUpsellCrossSell</t>
         </is>
       </c>
-      <c r="I444" s="4" t="inlineStr"/>
+      <c r="I444" s="2" t="inlineStr"/>
+      <c r="J444" s="4" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="6" t="inlineStr">
@@ -18890,7 +19534,8 @@
           <t>listCustomerSegmentChannel</t>
         </is>
       </c>
-      <c r="I445" s="4" t="inlineStr"/>
+      <c r="I445" s="5" t="inlineStr"/>
+      <c r="J445" s="4" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
@@ -18927,7 +19572,8 @@
           <t>listIncrementalityAttributionCannibalization</t>
         </is>
       </c>
-      <c r="I446" s="4" t="inlineStr"/>
+      <c r="I446" s="2" t="inlineStr"/>
+      <c r="J446" s="4" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="6" t="inlineStr">
@@ -18964,7 +19610,8 @@
           <t>listNextBestAction</t>
         </is>
       </c>
-      <c r="I447" s="4" t="inlineStr"/>
+      <c r="I447" s="5" t="inlineStr"/>
+      <c r="J447" s="4" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
@@ -19001,7 +19648,8 @@
           <t>listExecutivePromotionReporting</t>
         </is>
       </c>
-      <c r="I448" s="4" t="inlineStr"/>
+      <c r="I448" s="2" t="inlineStr"/>
+      <c r="J448" s="4" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="6" t="inlineStr">
@@ -19038,7 +19686,8 @@
           <t>listRuleWorkflow</t>
         </is>
       </c>
-      <c r="I449" s="4" t="inlineStr"/>
+      <c r="I449" s="5" t="inlineStr"/>
+      <c r="J449" s="4" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -19075,7 +19724,8 @@
           <t>setVisualBusinessRule</t>
         </is>
       </c>
-      <c r="I450" s="4" t="inlineStr"/>
+      <c r="I450" s="2" t="inlineStr"/>
+      <c r="J450" s="4" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="6" t="inlineStr">
@@ -19112,7 +19762,8 @@
           <t>listConditionDecisionLogic</t>
         </is>
       </c>
-      <c r="I451" s="4" t="inlineStr"/>
+      <c r="I451" s="5" t="inlineStr"/>
+      <c r="J451" s="4" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
@@ -19149,7 +19800,8 @@
           <t>setVisualWorkflow</t>
         </is>
       </c>
-      <c r="I452" s="4" t="inlineStr"/>
+      <c r="I452" s="2" t="inlineStr"/>
+      <c r="J452" s="4" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="6" t="inlineStr">
@@ -19186,7 +19838,8 @@
           <t>approveMatrixMultiLevel</t>
         </is>
       </c>
-      <c r="I453" s="4" t="inlineStr"/>
+      <c r="I453" s="5" t="inlineStr"/>
+      <c r="J453" s="4" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -19223,7 +19876,8 @@
           <t>approveRoleAuthorityDelegation</t>
         </is>
       </c>
-      <c r="I454" s="4" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr"/>
+      <c r="J454" s="4" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="6" t="inlineStr">
@@ -19260,7 +19914,8 @@
           <t>listSlaEscalationReminder</t>
         </is>
       </c>
-      <c r="I455" s="4" t="inlineStr"/>
+      <c r="I455" s="5" t="inlineStr"/>
+      <c r="J455" s="4" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
@@ -19297,7 +19952,8 @@
           <t>setTriggerActionCross</t>
         </is>
       </c>
-      <c r="I456" s="4" t="inlineStr"/>
+      <c r="I456" s="2" t="inlineStr"/>
+      <c r="J456" s="4" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="6" t="inlineStr">
@@ -19334,7 +19990,8 @@
           <t>simulateWorkflowTestingImpact</t>
         </is>
       </c>
-      <c r="I457" s="4" t="inlineStr"/>
+      <c r="I457" s="5" t="inlineStr"/>
+      <c r="J457" s="4" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -19371,7 +20028,8 @@
           <t>approveVersioningGovernance</t>
         </is>
       </c>
-      <c r="I458" s="4" t="inlineStr"/>
+      <c r="I458" s="2" t="inlineStr"/>
+      <c r="J458" s="4" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="6" t="inlineStr">
@@ -19408,7 +20066,8 @@
           <t>listWorkflow</t>
         </is>
       </c>
-      <c r="I459" s="4" t="inlineStr"/>
+      <c r="I459" s="5" t="inlineStr"/>
+      <c r="J459" s="4" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
@@ -19445,7 +20104,8 @@
           <t>approveUnifiedDecision</t>
         </is>
       </c>
-      <c r="I460" s="4" t="inlineStr"/>
+      <c r="I460" s="2" t="inlineStr"/>
+      <c r="J460" s="4" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="6" t="inlineStr">
@@ -19482,7 +20142,8 @@
           <t>listWorkflowInstanceProcess</t>
         </is>
       </c>
-      <c r="I461" s="4" t="inlineStr"/>
+      <c r="I461" s="5" t="inlineStr"/>
+      <c r="J461" s="4" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
@@ -19519,7 +20180,8 @@
           <t>listWorkflowExceptionFailure</t>
         </is>
       </c>
-      <c r="I462" s="4" t="inlineStr"/>
+      <c r="I462" s="2" t="inlineStr"/>
+      <c r="J462" s="4" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="6" t="inlineStr">
@@ -19556,7 +20218,8 @@
           <t>listSlaEscalationBottleneck</t>
         </is>
       </c>
-      <c r="I463" s="4" t="inlineStr"/>
+      <c r="I463" s="5" t="inlineStr"/>
+      <c r="J463" s="4" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
@@ -19593,7 +20256,8 @@
           <t>createAutomationAutonomouAction</t>
         </is>
       </c>
-      <c r="I464" s="4" t="inlineStr"/>
+      <c r="I464" s="2" t="inlineStr"/>
+      <c r="J464" s="4" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="6" t="inlineStr">
@@ -19630,7 +20294,8 @@
           <t>listCrossModuleOrchestration</t>
         </is>
       </c>
-      <c r="I465" s="4" t="inlineStr"/>
+      <c r="I465" s="5" t="inlineStr"/>
+      <c r="J465" s="4" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
@@ -19667,7 +20332,8 @@
           <t>listWorkflowProcessPerformance</t>
         </is>
       </c>
-      <c r="I466" s="4" t="inlineStr"/>
+      <c r="I466" s="2" t="inlineStr"/>
+      <c r="J466" s="4" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="6" t="inlineStr">
@@ -19704,7 +20370,8 @@
           <t>listProcessAutomationOpportunity</t>
         </is>
       </c>
-      <c r="I467" s="4" t="inlineStr"/>
+      <c r="I467" s="5" t="inlineStr"/>
+      <c r="J467" s="4" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
@@ -19741,7 +20408,8 @@
           <t>listWorkflowAutonomouGovernance</t>
         </is>
       </c>
-      <c r="I468" s="4" t="inlineStr"/>
+      <c r="I468" s="2" t="inlineStr"/>
+      <c r="J468" s="4" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="6" t="inlineStr">
@@ -19778,7 +20446,8 @@
           <t>listSaleChannel</t>
         </is>
       </c>
-      <c r="I469" s="4" t="inlineStr"/>
+      <c r="I469" s="5" t="inlineStr"/>
+      <c r="J469" s="4" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
@@ -19815,7 +20484,8 @@
           <t>createChannelProfile</t>
         </is>
       </c>
-      <c r="I470" s="4" t="inlineStr"/>
+      <c r="I470" s="2" t="inlineStr"/>
+      <c r="J470" s="4" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="6" t="inlineStr">
@@ -19852,7 +20522,8 @@
           <t>setProductCatalogue</t>
         </is>
       </c>
-      <c r="I471" s="4" t="inlineStr"/>
+      <c r="I471" s="5" t="inlineStr"/>
+      <c r="J471" s="4" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
@@ -19889,7 +20560,8 @@
           <t>setChannelPricingCommercial</t>
         </is>
       </c>
-      <c r="I472" s="4" t="inlineStr"/>
+      <c r="I472" s="2" t="inlineStr"/>
+      <c r="J472" s="4" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="6" t="inlineStr">
@@ -19926,7 +20598,8 @@
           <t>listInventoryCapacityChannel</t>
         </is>
       </c>
-      <c r="I473" s="4" t="inlineStr"/>
+      <c r="I473" s="5" t="inlineStr"/>
+      <c r="J473" s="4" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
@@ -19963,7 +20636,8 @@
           <t>listChannelSaleSchedule</t>
         </is>
       </c>
-      <c r="I474" s="4" t="inlineStr"/>
+      <c r="I474" s="2" t="inlineStr"/>
+      <c r="J474" s="4" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="6" t="inlineStr">
@@ -20000,7 +20674,8 @@
           <t>listCustomerEligibilityRule</t>
         </is>
       </c>
-      <c r="I475" s="4" t="inlineStr"/>
+      <c r="I475" s="5" t="inlineStr"/>
+      <c r="J475" s="4" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
@@ -20037,7 +20712,8 @@
           <t>listChannelSaleRule</t>
         </is>
       </c>
-      <c r="I476" s="4" t="inlineStr"/>
+      <c r="I476" s="2" t="inlineStr"/>
+      <c r="J476" s="4" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="6" t="inlineStr">
@@ -20074,7 +20750,8 @@
           <t>setChannelFeePayment</t>
         </is>
       </c>
-      <c r="I477" s="4" t="inlineStr"/>
+      <c r="I477" s="5" t="inlineStr"/>
+      <c r="J477" s="4" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
@@ -20111,7 +20788,8 @@
           <t>publishChannelReadinessValidation</t>
         </is>
       </c>
-      <c r="I478" s="4" t="inlineStr"/>
+      <c r="I478" s="2" t="inlineStr"/>
+      <c r="J478" s="4" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="6" t="inlineStr">
@@ -20148,7 +20826,8 @@
           <t>listChannel</t>
         </is>
       </c>
-      <c r="I479" s="4" t="inlineStr"/>
+      <c r="I479" s="5" t="inlineStr"/>
+      <c r="J479" s="4" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
@@ -20185,7 +20864,8 @@
           <t>listChannelConnectionIntegration</t>
         </is>
       </c>
-      <c r="I480" s="4" t="inlineStr"/>
+      <c r="I480" s="2" t="inlineStr"/>
+      <c r="J480" s="4" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="6" t="inlineStr">
@@ -20222,7 +20902,8 @@
           <t>listProductPriceAvailability</t>
         </is>
       </c>
-      <c r="I481" s="4" t="inlineStr"/>
+      <c r="I481" s="5" t="inlineStr"/>
+      <c r="J481" s="4" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
@@ -20259,7 +20940,8 @@
           <t>listRealTimeChannel</t>
         </is>
       </c>
-      <c r="I482" s="4" t="inlineStr"/>
+      <c r="I482" s="2" t="inlineStr"/>
+      <c r="J482" s="4" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="6" t="inlineStr">
@@ -20296,7 +20978,8 @@
           <t>listChannelAllocationRebalancing</t>
         </is>
       </c>
-      <c r="I483" s="4" t="inlineStr"/>
+      <c r="I483" s="5" t="inlineStr"/>
+      <c r="J483" s="4" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
@@ -20333,7 +21016,8 @@
           <t>listChannelExceptionIncident</t>
         </is>
       </c>
-      <c r="I484" s="4" t="inlineStr"/>
+      <c r="I484" s="2" t="inlineStr"/>
+      <c r="J484" s="4" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="6" t="inlineStr">
@@ -20370,7 +21054,8 @@
           <t>listChannelPerformanceCommercial</t>
         </is>
       </c>
-      <c r="I485" s="4" t="inlineStr"/>
+      <c r="I485" s="5" t="inlineStr"/>
+      <c r="J485" s="4" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
@@ -20407,7 +21092,8 @@
           <t>listChannelLogTransaction</t>
         </is>
       </c>
-      <c r="I486" s="4" t="inlineStr"/>
+      <c r="I486" s="2" t="inlineStr"/>
+      <c r="J486" s="4" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="6" t="inlineStr">
@@ -20444,7 +21130,8 @@
           <t>listChannelGovernanceSla</t>
         </is>
       </c>
-      <c r="I487" s="4" t="inlineStr"/>
+      <c r="I487" s="5" t="inlineStr"/>
+      <c r="J487" s="4" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
@@ -20481,7 +21168,8 @@
           <t>listChannel2</t>
         </is>
       </c>
-      <c r="I488" s="4" t="inlineStr"/>
+      <c r="I488" s="2" t="inlineStr"/>
+      <c r="J488" s="4" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="6" t="inlineStr">
@@ -20518,7 +21206,8 @@
           <t>listVirtualTicket</t>
         </is>
       </c>
-      <c r="I489" s="4" t="inlineStr"/>
+      <c r="I489" s="5" t="inlineStr"/>
+      <c r="J489" s="4" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
@@ -20555,7 +21244,8 @@
           <t>setVirtualTicketIdentity</t>
         </is>
       </c>
-      <c r="I490" s="4" t="inlineStr"/>
+      <c r="I490" s="2" t="inlineStr"/>
+      <c r="J490" s="4" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
@@ -20592,7 +21282,8 @@
           <t>listVirtualTicketStatus</t>
         </is>
       </c>
-      <c r="I491" s="4" t="inlineStr"/>
+      <c r="I491" s="5" t="inlineStr"/>
+      <c r="J491" s="4" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
@@ -20629,7 +21320,8 @@
           <t>listMediaTypeCredential</t>
         </is>
       </c>
-      <c r="I492" s="4" t="inlineStr"/>
+      <c r="I492" s="2" t="inlineStr"/>
+      <c r="J492" s="4" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="6" t="inlineStr">
@@ -20666,7 +21358,8 @@
           <t>listMultiMediaBinding</t>
         </is>
       </c>
-      <c r="I493" s="4" t="inlineStr"/>
+      <c r="I493" s="5" t="inlineStr"/>
+      <c r="J493" s="4" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -20703,7 +21396,8 @@
           <t>listCredentialIdentityToken</t>
         </is>
       </c>
-      <c r="I494" s="4" t="inlineStr"/>
+      <c r="I494" s="2" t="inlineStr"/>
+      <c r="J494" s="4" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="6" t="inlineStr">
@@ -20740,7 +21434,8 @@
           <t>listEntitlementCrossMedia</t>
         </is>
       </c>
-      <c r="I495" s="4" t="inlineStr"/>
+      <c r="I495" s="5" t="inlineStr"/>
+      <c r="J495" s="4" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -20777,7 +21472,8 @@
           <t>listMediaActivationPriority</t>
         </is>
       </c>
-      <c r="I496" s="4" t="inlineStr"/>
+      <c r="I496" s="2" t="inlineStr"/>
+      <c r="J496" s="4" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="6" t="inlineStr">
@@ -20814,7 +21510,8 @@
           <t>listMediaReplacementRevocation</t>
         </is>
       </c>
-      <c r="I497" s="4" t="inlineStr"/>
+      <c r="I497" s="5" t="inlineStr"/>
+      <c r="J497" s="4" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
@@ -20851,7 +21548,8 @@
           <t>listVirtualTicketArchitecture</t>
         </is>
       </c>
-      <c r="I498" s="4" t="inlineStr"/>
+      <c r="I498" s="2" t="inlineStr"/>
+      <c r="J498" s="4" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="6" t="inlineStr">
@@ -20888,7 +21586,8 @@
           <t>listMediaDesign</t>
         </is>
       </c>
-      <c r="I499" s="4" t="inlineStr"/>
+      <c r="I499" s="5" t="inlineStr"/>
+      <c r="J499" s="4" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
@@ -20925,7 +21624,8 @@
           <t>setDigitalBarcodeTicket</t>
         </is>
       </c>
-      <c r="I500" s="4" t="inlineStr"/>
+      <c r="I500" s="2" t="inlineStr"/>
+      <c r="J500" s="4" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="6" t="inlineStr">
@@ -20962,7 +21662,8 @@
           <t>setPdfPrintablePos</t>
         </is>
       </c>
-      <c r="I501" s="4" t="inlineStr"/>
+      <c r="I501" s="5" t="inlineStr"/>
+      <c r="J501" s="4" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
@@ -20999,7 +21700,8 @@
           <t>setAppleWalletPass</t>
         </is>
       </c>
-      <c r="I502" s="4" t="inlineStr"/>
+      <c r="I502" s="2" t="inlineStr"/>
+      <c r="J502" s="4" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="6" t="inlineStr">
@@ -21036,7 +21738,8 @@
           <t>setGoogleWalletPass</t>
         </is>
       </c>
-      <c r="I503" s="4" t="inlineStr"/>
+      <c r="I503" s="5" t="inlineStr"/>
+      <c r="J503" s="4" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
@@ -21073,7 +21776,8 @@
           <t>setRfidNfcCard</t>
         </is>
       </c>
-      <c r="I504" s="4" t="inlineStr"/>
+      <c r="I504" s="2" t="inlineStr"/>
+      <c r="J504" s="4" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
@@ -21110,7 +21814,8 @@
           <t>setDigitalCardMembership</t>
         </is>
       </c>
-      <c r="I505" s="4" t="inlineStr"/>
+      <c r="I505" s="5" t="inlineStr"/>
+      <c r="J505" s="4" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
@@ -21147,7 +21852,8 @@
           <t>setDynamicFieldData</t>
         </is>
       </c>
-      <c r="I506" s="4" t="inlineStr"/>
+      <c r="I506" s="2" t="inlineStr"/>
+      <c r="J506" s="4" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="6" t="inlineStr">
@@ -21184,7 +21890,8 @@
           <t>listBrandingLocalizationTemplate</t>
         </is>
       </c>
-      <c r="I507" s="4" t="inlineStr"/>
+      <c r="I507" s="5" t="inlineStr"/>
+      <c r="J507" s="4" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
@@ -21221,7 +21928,8 @@
           <t>approveMultiMediaPreview</t>
         </is>
       </c>
-      <c r="I508" s="4" t="inlineStr"/>
+      <c r="I508" s="2" t="inlineStr"/>
+      <c r="J508" s="4" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="6" t="inlineStr">
@@ -21258,7 +21966,8 @@
           <t>listCredential</t>
         </is>
       </c>
-      <c r="I509" s="4" t="inlineStr"/>
+      <c r="I509" s="5" t="inlineStr"/>
+      <c r="J509" s="4" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
@@ -21295,7 +22004,8 @@
           <t>setVirtualTicketCredential</t>
         </is>
       </c>
-      <c r="I510" s="4" t="inlineStr"/>
+      <c r="I510" s="2" t="inlineStr"/>
+      <c r="J510" s="4" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
@@ -21332,7 +22042,8 @@
           <t>listCredentialGenerationIssuance</t>
         </is>
       </c>
-      <c r="I511" s="4" t="inlineStr"/>
+      <c r="I511" s="5" t="inlineStr"/>
+      <c r="J511" s="4" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
@@ -21369,7 +22080,8 @@
           <t>listCredentialDeliveryDistribution</t>
         </is>
       </c>
-      <c r="I512" s="4" t="inlineStr"/>
+      <c r="I512" s="2" t="inlineStr"/>
+      <c r="J512" s="4" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="6" t="inlineStr">
@@ -21406,7 +22118,8 @@
           <t>setMediaBindingActivation</t>
         </is>
       </c>
-      <c r="I513" s="4" t="inlineStr"/>
+      <c r="I513" s="5" t="inlineStr"/>
+      <c r="J513" s="4" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
@@ -21443,7 +22156,8 @@
           <t>listCredentialReplacementReissue</t>
         </is>
       </c>
-      <c r="I514" s="4" t="inlineStr"/>
+      <c r="I514" s="2" t="inlineStr"/>
+      <c r="J514" s="4" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="6" t="inlineStr">
@@ -21480,7 +22194,8 @@
           <t>listFailedGenerationDelivery</t>
         </is>
       </c>
-      <c r="I515" s="4" t="inlineStr"/>
+      <c r="I515" s="5" t="inlineStr"/>
+      <c r="J515" s="4" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
@@ -21517,7 +22232,8 @@
           <t>listCredentialUsageCross</t>
         </is>
       </c>
-      <c r="I516" s="4" t="inlineStr"/>
+      <c r="I516" s="2" t="inlineStr"/>
+      <c r="J516" s="4" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="6" t="inlineStr">
@@ -21554,7 +22270,8 @@
           <t>listCredentialSecurityOperational</t>
         </is>
       </c>
-      <c r="I517" s="4" t="inlineStr"/>
+      <c r="I517" s="5" t="inlineStr"/>
+      <c r="J517" s="4" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
@@ -21591,7 +22308,8 @@
           <t>listTicketMedia</t>
         </is>
       </c>
-      <c r="I518" s="4" t="inlineStr"/>
+      <c r="I518" s="2" t="inlineStr"/>
+      <c r="J518" s="4" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="6" t="inlineStr">
@@ -21628,7 +22346,8 @@
           <t>listResaleMarketplace</t>
         </is>
       </c>
-      <c r="I519" s="4" t="inlineStr"/>
+      <c r="I519" s="5" t="inlineStr"/>
+      <c r="J519" s="4" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
@@ -21665,7 +22384,8 @@
           <t>setResaleEligibilityRule</t>
         </is>
       </c>
-      <c r="I520" s="4" t="inlineStr"/>
+      <c r="I520" s="2" t="inlineStr"/>
+      <c r="J520" s="4" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="6" t="inlineStr">
@@ -21702,7 +22422,8 @@
           <t>listResalePolicyMarketplace</t>
         </is>
       </c>
-      <c r="I521" s="4" t="inlineStr"/>
+      <c r="I521" s="5" t="inlineStr"/>
+      <c r="J521" s="4" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
@@ -21739,7 +22460,8 @@
           <t>createListingSeller</t>
         </is>
       </c>
-      <c r="I522" s="4" t="inlineStr"/>
+      <c r="I522" s="2" t="inlineStr"/>
+      <c r="J522" s="4" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="6" t="inlineStr">
@@ -21776,7 +22498,8 @@
           <t>listResalePricingPrice</t>
         </is>
       </c>
-      <c r="I523" s="4" t="inlineStr"/>
+      <c r="I523" s="5" t="inlineStr"/>
+      <c r="J523" s="4" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
@@ -21813,7 +22536,8 @@
           <t>listResaleFeeCommission</t>
         </is>
       </c>
-      <c r="I524" s="4" t="inlineStr"/>
+      <c r="I524" s="2" t="inlineStr"/>
+      <c r="J524" s="4" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="6" t="inlineStr">
@@ -21850,7 +22574,8 @@
           <t>approveListingModeration</t>
         </is>
       </c>
-      <c r="I525" s="4" t="inlineStr"/>
+      <c r="I525" s="5" t="inlineStr"/>
+      <c r="J525" s="4" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
@@ -21887,7 +22612,8 @@
           <t>listResaleInventoryAvailability</t>
         </is>
       </c>
-      <c r="I526" s="4" t="inlineStr"/>
+      <c r="I526" s="2" t="inlineStr"/>
+      <c r="J526" s="4" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="6" t="inlineStr">
@@ -21924,7 +22650,8 @@
           <t>listListingLifecycleExpiry</t>
         </is>
       </c>
-      <c r="I527" s="4" t="inlineStr"/>
+      <c r="I527" s="5" t="inlineStr"/>
+      <c r="J527" s="4" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
@@ -21961,7 +22688,8 @@
           <t>setResaleMarketplaceRecommendation</t>
         </is>
       </c>
-      <c r="I528" s="4" t="inlineStr"/>
+      <c r="I528" s="2" t="inlineStr"/>
+      <c r="J528" s="4" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="6" t="inlineStr">
@@ -21998,7 +22726,8 @@
           <t>listResale</t>
         </is>
       </c>
-      <c r="I529" s="4" t="inlineStr"/>
+      <c r="I529" s="5" t="inlineStr"/>
+      <c r="J529" s="4" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
@@ -22035,7 +22764,8 @@
           <t>listBuyerPurchaseResale</t>
         </is>
       </c>
-      <c r="I530" s="4" t="inlineStr"/>
+      <c r="I530" s="2" t="inlineStr"/>
+      <c r="J530" s="4" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="6" t="inlineStr">
@@ -22072,7 +22802,8 @@
           <t>listTicketOwnershipTransfer</t>
         </is>
       </c>
-      <c r="I531" s="4" t="inlineStr"/>
+      <c r="I531" s="5" t="inlineStr"/>
+      <c r="J531" s="4" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
@@ -22109,7 +22840,8 @@
           <t>listCredentialRevocationRegeneration</t>
         </is>
       </c>
-      <c r="I532" s="4" t="inlineStr"/>
+      <c r="I532" s="2" t="inlineStr"/>
+      <c r="J532" s="4" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="6" t="inlineStr">
@@ -22146,7 +22878,8 @@
           <t>listResaleFraudDuplicate</t>
         </is>
       </c>
-      <c r="I533" s="4" t="inlineStr"/>
+      <c r="I533" s="5" t="inlineStr"/>
+      <c r="J533" s="4" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
@@ -22183,7 +22916,8 @@
           <t>listCapacityInventoryReconciliation</t>
         </is>
       </c>
-      <c r="I534" s="4" t="inlineStr"/>
+      <c r="I534" s="2" t="inlineStr"/>
+      <c r="J534" s="4" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="6" t="inlineStr">
@@ -22220,7 +22954,8 @@
           <t>listSellerSettlementPayout</t>
         </is>
       </c>
-      <c r="I535" s="4" t="inlineStr"/>
+      <c r="I535" s="5" t="inlineStr"/>
+      <c r="J535" s="4" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
@@ -22257,7 +22992,8 @@
           <t>listRefundDisputeResale</t>
         </is>
       </c>
-      <c r="I536" s="4" t="inlineStr"/>
+      <c r="I536" s="2" t="inlineStr"/>
+      <c r="J536" s="4" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="6" t="inlineStr">
@@ -22294,7 +23030,8 @@
           <t>listResaleOwnership</t>
         </is>
       </c>
-      <c r="I537" s="4" t="inlineStr"/>
+      <c r="I537" s="5" t="inlineStr"/>
+      <c r="J537" s="4" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
@@ -22331,7 +23068,8 @@
           <t>listResale2</t>
         </is>
       </c>
-      <c r="I538" s="4" t="inlineStr"/>
+      <c r="I538" s="2" t="inlineStr"/>
+      <c r="J538" s="4" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="6" t="inlineStr">
@@ -22368,7 +23106,8 @@
           <t>listTicketResaleMarketplace</t>
         </is>
       </c>
-      <c r="I539" s="4" t="inlineStr"/>
+      <c r="I539" s="5" t="inlineStr"/>
+      <c r="J539" s="4" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
@@ -22405,7 +23144,8 @@
           <t>listResaleEligibilityTicket</t>
         </is>
       </c>
-      <c r="I540" s="4" t="inlineStr"/>
+      <c r="I540" s="2" t="inlineStr"/>
+      <c r="J540" s="4" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="6" t="inlineStr">
@@ -22442,7 +23182,8 @@
           <t>listCreateListingResale</t>
         </is>
       </c>
-      <c r="I541" s="4" t="inlineStr"/>
+      <c r="I541" s="5" t="inlineStr"/>
+      <c r="J541" s="4" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
@@ -22479,7 +23220,8 @@
           <t>listFeeSellerProceed</t>
         </is>
       </c>
-      <c r="I542" s="4" t="inlineStr"/>
+      <c r="I542" s="2" t="inlineStr"/>
+      <c r="J542" s="4" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="6" t="inlineStr">
@@ -22516,7 +23258,8 @@
           <t>listResaleListingSeller</t>
         </is>
       </c>
-      <c r="I543" s="4" t="inlineStr"/>
+      <c r="I543" s="5" t="inlineStr"/>
+      <c r="J543" s="4" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
@@ -22553,7 +23296,8 @@
           <t>listOfficialResaleMarketplace</t>
         </is>
       </c>
-      <c r="I544" s="4" t="inlineStr"/>
+      <c r="I544" s="2" t="inlineStr"/>
+      <c r="J544" s="4" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="6" t="inlineStr">
@@ -22590,7 +23334,8 @@
           <t>listResaleTicketDetail</t>
         </is>
       </c>
-      <c r="I545" s="4" t="inlineStr"/>
+      <c r="I545" s="5" t="inlineStr"/>
+      <c r="J545" s="4" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
@@ -22627,7 +23372,8 @@
           <t>listBuyerCheckoutInventory</t>
         </is>
       </c>
-      <c r="I546" s="4" t="inlineStr"/>
+      <c r="I546" s="2" t="inlineStr"/>
+      <c r="J546" s="4" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="6" t="inlineStr">
@@ -22664,7 +23410,8 @@
           <t>listResaleConfirmationOwnership</t>
         </is>
       </c>
-      <c r="I547" s="4" t="inlineStr"/>
+      <c r="I547" s="5" t="inlineStr"/>
+      <c r="J547" s="4" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
@@ -22701,7 +23448,8 @@
           <t>listWhiteLabelMarketplace</t>
         </is>
       </c>
-      <c r="I548" s="4" t="inlineStr"/>
+      <c r="I548" s="2" t="inlineStr"/>
+      <c r="J548" s="4" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="6" t="inlineStr">
@@ -22738,7 +23486,8 @@
           <t>listUpgradeConversion</t>
         </is>
       </c>
-      <c r="I549" s="4" t="inlineStr"/>
+      <c r="I549" s="5" t="inlineStr"/>
+      <c r="J549" s="4" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
@@ -22775,7 +23524,8 @@
           <t>setUpgradeConversionPath</t>
         </is>
       </c>
-      <c r="I550" s="4" t="inlineStr"/>
+      <c r="I550" s="2" t="inlineStr"/>
+      <c r="J550" s="4" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="6" t="inlineStr">
@@ -22812,7 +23562,8 @@
           <t>listUpgradeEligibilityQualification</t>
         </is>
       </c>
-      <c r="I551" s="4" t="inlineStr"/>
+      <c r="I551" s="5" t="inlineStr"/>
+      <c r="J551" s="4" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
@@ -22849,7 +23600,8 @@
           <t>listUpgradeTimingUsage</t>
         </is>
       </c>
-      <c r="I552" s="4" t="inlineStr"/>
+      <c r="I552" s="2" t="inlineStr"/>
+      <c r="J552" s="4" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="6" t="inlineStr">
@@ -22886,7 +23638,8 @@
           <t>listUpgradeFinancialTreatment</t>
         </is>
       </c>
-      <c r="I553" s="4" t="inlineStr"/>
+      <c r="I553" s="5" t="inlineStr"/>
+      <c r="J553" s="4" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
@@ -22923,7 +23676,8 @@
           <t>setProRataResidual</t>
         </is>
       </c>
-      <c r="I554" s="4" t="inlineStr"/>
+      <c r="I554" s="2" t="inlineStr"/>
+      <c r="J554" s="4" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="6" t="inlineStr">
@@ -22960,7 +23714,8 @@
           <t>listPersonTypeProduct</t>
         </is>
       </c>
-      <c r="I555" s="4" t="inlineStr"/>
+      <c r="I555" s="5" t="inlineStr"/>
+      <c r="J555" s="4" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
@@ -22997,7 +23752,8 @@
           <t>listBulkGroupAssisted</t>
         </is>
       </c>
-      <c r="I556" s="4" t="inlineStr"/>
+      <c r="I556" s="2" t="inlineStr"/>
+      <c r="J556" s="4" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="6" t="inlineStr">
@@ -23034,7 +23790,8 @@
           <t>createUpgradeCredentialRegeneration</t>
         </is>
       </c>
-      <c r="I557" s="4" t="inlineStr"/>
+      <c r="I557" s="5" t="inlineStr"/>
+      <c r="J557" s="4" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
@@ -23071,7 +23828,8 @@
           <t>listUpgradeException</t>
         </is>
       </c>
-      <c r="I558" s="4" t="inlineStr"/>
+      <c r="I558" s="2" t="inlineStr"/>
+      <c r="J558" s="4" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="6" t="inlineStr">
@@ -23108,7 +23866,8 @@
           <t>listWaiverConsent</t>
         </is>
       </c>
-      <c r="I559" s="4" t="inlineStr"/>
+      <c r="I559" s="5" t="inlineStr"/>
+      <c r="J559" s="4" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
@@ -23145,7 +23904,8 @@
           <t>listWaiverTemplateMaster</t>
         </is>
       </c>
-      <c r="I560" s="4" t="inlineStr"/>
+      <c r="I560" s="2" t="inlineStr"/>
+      <c r="J560" s="4" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="6" t="inlineStr">
@@ -23182,7 +23942,8 @@
           <t>setDigitalWaiverForm</t>
         </is>
       </c>
-      <c r="I561" s="4" t="inlineStr"/>
+      <c r="I561" s="5" t="inlineStr"/>
+      <c r="J561" s="4" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
@@ -23219,7 +23980,8 @@
           <t>listDynamicFieldQuestion</t>
         </is>
       </c>
-      <c r="I562" s="4" t="inlineStr"/>
+      <c r="I562" s="2" t="inlineStr"/>
+      <c r="J562" s="4" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="6" t="inlineStr">
@@ -23256,7 +24018,8 @@
           <t>setSignatorySignatureGuardian</t>
         </is>
       </c>
-      <c r="I563" s="4" t="inlineStr"/>
+      <c r="I563" s="5" t="inlineStr"/>
+      <c r="J563" s="4" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
@@ -23293,7 +24056,8 @@
           <t>listProductEventExperience</t>
         </is>
       </c>
-      <c r="I564" s="4" t="inlineStr"/>
+      <c r="I564" s="2" t="inlineStr"/>
+      <c r="J564" s="4" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="6" t="inlineStr">
@@ -23330,7 +24094,8 @@
           <t>listWaiverTriggerEligibility</t>
         </is>
       </c>
-      <c r="I565" s="4" t="inlineStr"/>
+      <c r="I565" s="5" t="inlineStr"/>
+      <c r="J565" s="4" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
@@ -23367,7 +24132,8 @@
           <t>listVersioningEffectiveDate</t>
         </is>
       </c>
-      <c r="I566" s="4" t="inlineStr"/>
+      <c r="I566" s="2" t="inlineStr"/>
+      <c r="J566" s="4" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="6" t="inlineStr">
@@ -23404,7 +24170,8 @@
           <t>setLocalizationBrandingCustomer</t>
         </is>
       </c>
-      <c r="I567" s="4" t="inlineStr"/>
+      <c r="I567" s="5" t="inlineStr"/>
+      <c r="J567" s="4" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
@@ -23441,7 +24208,8 @@
           <t>approveWaiverTesting</t>
         </is>
       </c>
-      <c r="I568" s="4" t="inlineStr"/>
+      <c r="I568" s="2" t="inlineStr"/>
+      <c r="J568" s="4" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="6" t="inlineStr">
@@ -23478,7 +24246,8 @@
           <t>listWaiver</t>
         </is>
       </c>
-      <c r="I569" s="4" t="inlineStr"/>
+      <c r="I569" s="5" t="inlineStr"/>
+      <c r="J569" s="4" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
@@ -23515,7 +24284,8 @@
           <t>listParticipantWaiverStatus</t>
         </is>
       </c>
-      <c r="I570" s="4" t="inlineStr"/>
+      <c r="I570" s="2" t="inlineStr"/>
+      <c r="J570" s="4" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="6" t="inlineStr">
@@ -23552,7 +24322,8 @@
           <t>listDigitalSigningCollection</t>
         </is>
       </c>
-      <c r="I571" s="4" t="inlineStr"/>
+      <c r="I571" s="5" t="inlineStr"/>
+      <c r="J571" s="4" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
@@ -23589,7 +24360,8 @@
           <t>listMinorGuardianGroup</t>
         </is>
       </c>
-      <c r="I572" s="4" t="inlineStr"/>
+      <c r="I572" s="2" t="inlineStr"/>
+      <c r="J572" s="4" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="6" t="inlineStr">
@@ -23626,7 +24398,8 @@
           <t>setWaiverVerificationValidation</t>
         </is>
       </c>
-      <c r="I573" s="4" t="inlineStr"/>
+      <c r="I573" s="5" t="inlineStr"/>
+      <c r="J573" s="4" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
@@ -23663,7 +24436,8 @@
           <t>listMissingExpiredInvalid</t>
         </is>
       </c>
-      <c r="I574" s="4" t="inlineStr"/>
+      <c r="I574" s="2" t="inlineStr"/>
+      <c r="J574" s="4" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="6" t="inlineStr">
@@ -23700,7 +24474,8 @@
           <t>listSiteWaiverException</t>
         </is>
       </c>
-      <c r="I575" s="4" t="inlineStr"/>
+      <c r="I575" s="5" t="inlineStr"/>
+      <c r="J575" s="4" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
@@ -23737,7 +24512,8 @@
           <t>listComplianceEvidenceWaiver</t>
         </is>
       </c>
-      <c r="I576" s="4" t="inlineStr"/>
+      <c r="I576" s="2" t="inlineStr"/>
+      <c r="J576" s="4" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="6" t="inlineStr">
@@ -23774,7 +24550,8 @@
           <t>listWaiverComplianceOperational</t>
         </is>
       </c>
-      <c r="I577" s="4" t="inlineStr"/>
+      <c r="I577" s="5" t="inlineStr"/>
+      <c r="J577" s="4" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
@@ -23811,10 +24588,11 @@
           <t>listWaiverComplianceRisk</t>
         </is>
       </c>
-      <c r="I578" s="4" t="inlineStr"/>
+      <c r="I578" s="2" t="inlineStr"/>
+      <c r="J578" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 27% of the 2113 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 27% of the 2135 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management: confirm the 30 screens we drafted from pages 4, 6, 8-9, 11-12, 14-17, 23-24, 26-27, 29-32, 34, 36, 41, 43, 45, 47-48, 50-51, 53-54, 56. We read 922 of your bullets as fields and set aside 478 as prose - were any of those 478 actually fields?</t>
+          <t>Ticket Media &amp; Credential Management: confirm the 30 screens we drafted from pages 4, 6, 8-9, 11-12, 14-17, 23-24, 26-27, 29-32, 34, 36, 41, 43, 45, 47-48, 50-51, 53-54, 56. We read 922 of your bullets as fields and set aside 478 as prose - were any of those 478 actually fields?</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Manage guests temporarily leaving and returning to the venue. 106 | Pa ge The source matrix requires configurable re-entry and also describes a journey using a designated re-entry gate with both ticket verification and a UV stamp.</t>
+          <t>Manage guests temporarily leaving and returning to the venue. The source matrix requires configurable re-entry and also describes a journey using a designated re-entry gate with both ticket verification and a UV stamp.</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -21174,7 +21174,7 @@
     <row r="489">
       <c r="A489" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B489" s="6" t="n">
@@ -21212,7 +21212,7 @@
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B490" s="3" t="n">
@@ -21250,7 +21250,7 @@
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B491" s="6" t="n">
@@ -21288,7 +21288,7 @@
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B492" s="3" t="n">
@@ -21326,7 +21326,7 @@
     <row r="493">
       <c r="A493" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B493" s="6" t="n">
@@ -21364,7 +21364,7 @@
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B494" s="3" t="n">
@@ -21402,7 +21402,7 @@
     <row r="495">
       <c r="A495" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B495" s="6" t="n">
@@ -21440,7 +21440,7 @@
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B496" s="3" t="n">
@@ -21478,7 +21478,7 @@
     <row r="497">
       <c r="A497" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B497" s="6" t="n">
@@ -21516,7 +21516,7 @@
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B498" s="3" t="n">
@@ -21554,7 +21554,7 @@
     <row r="499">
       <c r="A499" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B499" s="6" t="n">
@@ -21592,7 +21592,7 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B500" s="3" t="n">
@@ -21630,7 +21630,7 @@
     <row r="501">
       <c r="A501" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B501" s="6" t="n">
@@ -21668,7 +21668,7 @@
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B502" s="3" t="n">
@@ -21706,7 +21706,7 @@
     <row r="503">
       <c r="A503" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B503" s="6" t="n">
@@ -21744,7 +21744,7 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B504" s="3" t="n">
@@ -21782,7 +21782,7 @@
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B505" s="6" t="n">
@@ -21820,7 +21820,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B506" s="3" t="n">
@@ -21858,7 +21858,7 @@
     <row r="507">
       <c r="A507" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B507" s="6" t="n">
@@ -21896,7 +21896,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B508" s="3" t="n">
@@ -21934,7 +21934,7 @@
     <row r="509">
       <c r="A509" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B509" s="6" t="n">
@@ -21972,7 +21972,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B510" s="3" t="n">
@@ -22010,7 +22010,7 @@
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B511" s="6" t="n">
@@ -22048,7 +22048,7 @@
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B512" s="3" t="n">
@@ -22086,7 +22086,7 @@
     <row r="513">
       <c r="A513" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B513" s="6" t="n">
@@ -22124,7 +22124,7 @@
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B514" s="3" t="n">
@@ -22162,7 +22162,7 @@
     <row r="515">
       <c r="A515" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B515" s="6" t="n">
@@ -22200,7 +22200,7 @@
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B516" s="3" t="n">
@@ -22238,7 +22238,7 @@
     <row r="517">
       <c r="A517" s="6" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B517" s="6" t="n">
@@ -22276,7 +22276,7 @@
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
         <is>
-          <t>Ticket Media Credential Management</t>
+          <t>Ticket Media &amp; Credential Management</t>
         </is>
       </c>
       <c r="B518" s="3" t="n">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 27% of the 2135 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 27% of the 2147 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2298 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2405 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4079,75 +4079,6 @@
       </c>
       <c r="E104" s="4" t="inlineStr"/>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>ACC-002</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>Registration Form</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>ACC-003</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Application Review &amp; Submit</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>ACC-004</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>Application Status Tracking</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2608 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2660 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2660 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2668 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2668 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2731 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>P09 (1)</t>
+          <t>P08 (1)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Is the AI Configuration Assistant in this delivery? 0 screens - setup discovery, guided Q&amp;A, blueprint, execution, rollback and audit.</t>
+          <t>Is the AI Configuration Assistant in this delivery? 15 screens - setup discovery, guided Q&amp;A, blueprint, execution, rollback and audit.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Is Forecasting in this delivery? 0 screens with no operation behind them.</t>
+          <t>Is Forecasting in this delivery? 1 screens with no operation behind them.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Is AI governance in this delivery? 1 screens - capability registry, risk classification, policy builder, approval review.</t>
+          <t>Is AI governance in this delivery? 6 screens - capability registry, risk classification, policy builder, approval review.</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The ai contract has 31 operations in total, against 1 screens of AI product with nothing behind them.</t>
+          <t>The ai contract has 31 operations in total, against 22 screens of AI product with nothing behind them.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>P09 (1)</t>
+          <t>P08 (1)</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1713,22 +1713,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI governance and human oversight</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ADM-618</t>
+          <t>ADM-121</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Refund Simulator, Risk Analysis &amp; AI Advisor\t126</t>
+          <t>Bulk Product Creation &amp; Catalogue Import</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
@@ -1736,22 +1736,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>GST-043</t>
+          <t>ADM-242</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Arabic / RTL Experience</t>
+          <t>Approval Matrix &amp; Multi-Level Approval Configuration</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -1759,22 +1759,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>KSK-001</t>
+          <t>ADM-353</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Attract Loop</t>
+          <t>Webhook Configuration &amp; Subscription Manager</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -1782,22 +1782,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>KSK-014</t>
+          <t>ADM-611</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Out of service</t>
+          <t>Refund Policy &amp; Rule Configuration</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -1805,22 +1805,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>EMP-044</t>
+          <t>BO-1161</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Security Rules Testing, Simulation &amp; AI Sandbox</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1828,22 +1828,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>EMP-045</t>
+          <t>BO-1174</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Arabic / RTL</t>
+          <t>Wallet API Catalogue &amp; Endpoint Configuration</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1851,25 +1851,1405 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BO-389</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Reminder &amp; Breach Notification Rules</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>BO-390</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Escalation Policy Builder</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>BO-403</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Attraction Audit, Dependencies &amp; Governed Actions</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>BO-599</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Manual Configuration Center</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>BO-646</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Credential Media Configuration</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>BO-678</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Channel, Language &amp; Branding Configuration</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>BO-797</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>AI Chatbot Configuration</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>BO-817</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NPS, CSAT &amp; CES Configuration</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AI configuration assistant</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ADM-408</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Final Package Approval &amp; Handoff</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Forecasting</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>BO-1069</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Platform Health &amp; Observability</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AI governance and human oversight</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>ADM-618</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Refund Simulator, Risk Analysis &amp; AI Advisor</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>AI governance and human oversight</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>BO-1072</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Seat Management APIs</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AI governance and human oversight</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>BO-528</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Dynamic Pricing &amp; AI Recommendation</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>AI governance and human oversight</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>BO-824</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Gamification Command Center</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>AI governance and human oversight</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>BO-841</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Personalization &amp; Localization</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>AI governance and human oversight</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>BO-998</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Lock Timeout &amp; Concurrency</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KSK-001</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Attract Loop</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>KSK-014</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Out of service</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>EMP-044</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>EMP-045</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Arabic / RTL</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>ADM-097</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Rule Priority, Conflict Resolution &amp; Dynamic Pricing Test Console</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ADM-169</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Buy X Get Y / BOGO Rule Builder</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>ADM-172</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Fixed-Price &amp; “N for X” Offer Builder</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ADM-173</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Gift, Free Product &amp; Added-Value Offer Builder</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>ADM-174</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Cross-Category Promotion Builder</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ADM-199</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Eligibility Rule Builder</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>ADM-249</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Unified Approval Inbox &amp; Decision Workspace</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ADM-252</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>SLA, Escalation &amp; Bottleneck Monitor</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>ADM-344</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Digital Signature Management</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>BO-031</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Asset Register</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>BO-110</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Recipe &amp; BOM Management</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>BO-113</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Central Kitchen &amp; Commissary Management</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>BO-1133</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Wallet Usage &amp; Channel Command Center</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>BO-138</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Production Execution &amp; Batch Management</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>BO-365</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>My Approval Inbox</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>BO-432</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Real-Time Gameplay Authorization</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>BO-444</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Redemption Operations Dashboard</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>BO-458</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Expiry Monitoring &amp; Upcoming Expiration</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>BO-477</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Reader Command &amp; Event Mapping</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>BO-483</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Integration Certification &amp; Test Console</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>BO-484</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Self-Service Experience Command Center</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>BO-587</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Equipment Performance Analytics</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>BO-669</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Temporary &amp; Seasonal Accreditation</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>BO-674</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Accreditation Communications Command Center</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>BO-677</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Communication Template Library</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>BO-679</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Manual &amp; Bulk Communication Center</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>BO-681</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Import Validation &amp; Processing Monitor</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>BO-728</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Outlet Management</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>BO-729</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Create / Edit Outlet</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>BO-812</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Service Recovery</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>BO-822</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Service Recovery Automation</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>BO-838</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Content, Media &amp; Forms</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>BO-942</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Operations Control &amp; Offline Sync</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>ADM-375</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Renewal &amp; Retention Center</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>ADM-376</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Commercial Optimization &amp; Expansion Opportunities</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>ADM-379</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>ADM-409</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Purchase / Trial Journey Selection</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>ADM-464</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Renewal Management Center</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>ACC-001</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Landing / Programme Overview</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>SGN-001</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>SGN-018</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Purchase / Trial Journey Selection</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2731 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2738 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2738 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2758 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2224,17 +2224,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>KSK-001</t>
+          <t>EMP-044</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Attract Loop</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>KSK-014</t>
+          <t>EMP-045</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Out of service</t>
+          <t>Arabic / RTL</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2270,17 +2270,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>EMP-044</t>
+          <t>ADM-097</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Rule Priority, Conflict Resolution &amp; Dynamic Pricing Test Console</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2293,17 +2293,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>EMP-045</t>
+          <t>ADM-169</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Arabic / RTL</t>
+          <t>Buy X Get Y / BOGO Rule Builder</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ADM-097</t>
+          <t>ADM-172</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Rule Priority, Conflict Resolution &amp; Dynamic Pricing Test Console</t>
+          <t>Fixed-Price &amp; “N for X” Offer Builder</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>ADM-169</t>
+          <t>ADM-173</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Buy X Get Y / BOGO Rule Builder</t>
+          <t>Gift, Free Product &amp; Added-Value Offer Builder</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ADM-172</t>
+          <t>ADM-174</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Fixed-Price &amp; “N for X” Offer Builder</t>
+          <t>Cross-Category Promotion Builder</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>ADM-173</t>
+          <t>ADM-199</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Gift, Free Product &amp; Added-Value Offer Builder</t>
+          <t>Eligibility Rule Builder</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ADM-174</t>
+          <t>ADM-249</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Cross-Category Promotion Builder</t>
+          <t>Unified Approval Inbox &amp; Decision Workspace</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>ADM-199</t>
+          <t>ADM-252</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Eligibility Rule Builder</t>
+          <t>SLA, Escalation &amp; Bottleneck Monitor</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ADM-249</t>
+          <t>ADM-344</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Unified Approval Inbox &amp; Decision Workspace</t>
+          <t>Digital Signature Management</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>ADM-252</t>
+          <t>BO-031</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>SLA, Escalation &amp; Bottleneck Monitor</t>
+          <t>Asset Register</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ADM-344</t>
+          <t>BO-110</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Digital Signature Management</t>
+          <t>Recipe &amp; BOM Management</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>BO-031</t>
+          <t>BO-113</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Asset Register</t>
+          <t>Central Kitchen &amp; Commissary Management</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>BO-110</t>
+          <t>BO-1133</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Recipe &amp; BOM Management</t>
+          <t>Wallet Usage &amp; Channel Command Center</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>BO-113</t>
+          <t>BO-138</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Central Kitchen &amp; Commissary Management</t>
+          <t>Production Execution &amp; Batch Management</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>BO-1133</t>
+          <t>BO-365</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Wallet Usage &amp; Channel Command Center</t>
+          <t>My Approval Inbox</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BO-138</t>
+          <t>BO-432</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Production Execution &amp; Batch Management</t>
+          <t>Real-Time Gameplay Authorization</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>BO-365</t>
+          <t>BO-444</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>My Approval Inbox</t>
+          <t>Redemption Operations Dashboard</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>BO-432</t>
+          <t>BO-458</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Gameplay Authorization</t>
+          <t>Expiry Monitoring &amp; Upcoming Expiration</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>BO-444</t>
+          <t>BO-477</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Redemption Operations Dashboard</t>
+          <t>Reader Command &amp; Event Mapping</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>BO-458</t>
+          <t>BO-483</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Expiry Monitoring &amp; Upcoming Expiration</t>
+          <t>Integration Certification &amp; Test Console</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>BO-477</t>
+          <t>BO-484</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Reader Command &amp; Event Mapping</t>
+          <t>Self-Service Experience Command Center</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>BO-483</t>
+          <t>BO-587</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Integration Certification &amp; Test Console</t>
+          <t>Inventory &amp; Equipment Performance Analytics</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BO-484</t>
+          <t>BO-669</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Self-Service Experience Command Center</t>
+          <t>Temporary &amp; Seasonal Accreditation</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>BO-587</t>
+          <t>BO-674</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Inventory &amp; Equipment Performance Analytics</t>
+          <t>Accreditation Communications Command Center</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BO-669</t>
+          <t>BO-677</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Temporary &amp; Seasonal Accreditation</t>
+          <t>Communication Template Library</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>BO-674</t>
+          <t>BO-679</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Accreditation Communications Command Center</t>
+          <t>Manual &amp; Bulk Communication Center</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BO-677</t>
+          <t>BO-681</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Communication Template Library</t>
+          <t>Import Validation &amp; Processing Monitor</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>BO-679</t>
+          <t>BO-728</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Manual &amp; Bulk Communication Center</t>
+          <t>Outlet Management</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>BO-681</t>
+          <t>BO-729</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Import Validation &amp; Processing Monitor</t>
+          <t>Create / Edit Outlet</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>BO-728</t>
+          <t>BO-812</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Outlet Management</t>
+          <t>Service Recovery</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BO-729</t>
+          <t>BO-822</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Create / Edit Outlet</t>
+          <t>Service Recovery Automation</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>BO-812</t>
+          <t>BO-838</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Service Recovery</t>
+          <t>Content, Media &amp; Forms</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>BO-822</t>
+          <t>BO-942</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Service Recovery Automation</t>
+          <t>Mobile Operations Control &amp; Offline Sync</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3029,17 +3029,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>BO-838</t>
+          <t>ADM-375</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Content, Media &amp; Forms</t>
+          <t>Renewal &amp; Retention Center</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3052,17 +3052,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>BO-942</t>
+          <t>ADM-376</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Mobile Operations Control &amp; Offline Sync</t>
+          <t>Commercial Optimization &amp; Expansion Opportunities</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>ADM-375</t>
+          <t>ADM-379</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Renewal &amp; Retention Center</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ADM-376</t>
+          <t>ADM-409</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Commercial Optimization &amp; Expansion Opportunities</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>ADM-379</t>
+          <t>ADM-464</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
+          <t>Renewal Management Center</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ADM-409</t>
+          <t>ACC-001</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Purchase / Trial Journey Selection</t>
+          <t>Landing / Programme Overview</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3167,17 +3167,17 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>ADM-464</t>
+          <t>SGN-001</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Renewal Management Center</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3190,66 +3190,20 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>ACC-001</t>
+          <t>SGN-018</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Landing / Programme Overview</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>SGN-001</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>SGN-018</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Purchase / Trial Journey Selection</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2758 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2776 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BO-669</t>
+          <t>BO-674</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Temporary &amp; Seasonal Accreditation</t>
+          <t>Accreditation Communications Command Center</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>BO-674</t>
+          <t>BO-677</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Accreditation Communications Command Center</t>
+          <t>Communication Template Library</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BO-677</t>
+          <t>BO-679</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Communication Template Library</t>
+          <t>Manual &amp; Bulk Communication Center</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>BO-679</t>
+          <t>BO-681</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Manual &amp; Bulk Communication Center</t>
+          <t>Import Validation &amp; Processing Monitor</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BO-681</t>
+          <t>BO-728</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Import Validation &amp; Processing Monitor</t>
+          <t>Outlet Management</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>BO-728</t>
+          <t>BO-729</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Outlet Management</t>
+          <t>Create / Edit Outlet</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>BO-729</t>
+          <t>BO-812</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Create / Edit Outlet</t>
+          <t>Service Recovery</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>BO-812</t>
+          <t>BO-822</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Service Recovery</t>
+          <t>Service Recovery Automation</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BO-822</t>
+          <t>BO-838</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Service Recovery Automation</t>
+          <t>Content, Media &amp; Forms</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>BO-838</t>
+          <t>BO-942</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Content, Media &amp; Forms</t>
+          <t>Mobile Operations Control &amp; Offline Sync</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3006,17 +3006,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>BO-942</t>
+          <t>ADM-375</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Mobile Operations Control &amp; Offline Sync</t>
+          <t>Renewal &amp; Retention Center</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>ADM-375</t>
+          <t>ADM-376</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Renewal &amp; Retention Center</t>
+          <t>Commercial Optimization &amp; Expansion Opportunities</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ADM-376</t>
+          <t>ADM-379</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Commercial Optimization &amp; Expansion Opportunities</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>ADM-379</t>
+          <t>ADM-409</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ADM-409</t>
+          <t>ADM-464</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Purchase / Trial Journey Selection</t>
+          <t>Renewal Management Center</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3121,17 +3121,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>ADM-464</t>
+          <t>ACC-001</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Renewal Management Center</t>
+          <t>Landing / Programme Overview</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ACC-001</t>
+          <t>SGN-001</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Landing / Programme Overview</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3172,38 +3172,15 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>SGN-001</t>
+          <t>SGN-018</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>SGN-018</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Purchase / Trial Journey Selection</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2776 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2789 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2789 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2790 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2790 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2796 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2796 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2802 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2802 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2804 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ADM-375</t>
+          <t>ADM-379</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Renewal &amp; Retention Center</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>ADM-376</t>
+          <t>ADM-409</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Commercial Optimization &amp; Expansion Opportunities</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3052,17 +3052,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ADM-379</t>
+          <t>ACC-001</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
+          <t>Landing / Programme Overview</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3075,17 +3075,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>ADM-409</t>
+          <t>SGN-001</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Purchase / Trial Journey Selection</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3098,89 +3098,20 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ADM-464</t>
+          <t>SGN-018</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Renewal Management Center</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>ACC-001</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Landing / Programme Overview</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>SGN-001</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>SGN-018</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Purchase / Trial Journey Selection</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2804 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2844 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3113,6 +3113,52 @@
       </c>
       <c r="E62" s="4" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>SGN-019</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Contract &amp; Billing Cycle Selection</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>SGN-024</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Subscription Confirmation &amp; Commercial Activation</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2844 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2845 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2845 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2854 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">

--- a/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
+++ b/ticvai/repos/ticvai-infra/project-bible/handoff/TICVAI_Client_Questions.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>They are 0% of the 2854 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
+          <t>They are 0% of the 2857 operations and exactly the ones with no data lineage. Nothing behind them can be built until they are agreed.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Is the AI Configuration Assistant in this delivery? 15 screens - setup discovery, guided Q&amp;A, blueprint, execution, rollback and audit.</t>
+          <t>Is the AI Configuration Assistant in this delivery? 17 screens - setup discovery, guided Q&amp;A, blueprint, execution, rollback and audit.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The ai contract has 31 operations in total, against 22 screens of AI product with nothing behind them.</t>
+          <t>The ai contract has 31 operations in total, against 24 screens of AI product with nothing behind them.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>BO-646</t>
+          <t>BO-602</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Credential Media Configuration</t>
+          <t>POS, Payment &amp; Access Setup</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>BO-678</t>
+          <t>BO-646</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Channel, Language &amp; Branding Configuration</t>
+          <t>Credential Media Configuration</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>BO-797</t>
+          <t>BO-678</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>AI Chatbot Configuration</t>
+          <t>Channel, Language &amp; Branding Configuration</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>BO-817</t>
+          <t>BO-797</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>NPS, CSAT &amp; CES Configuration</t>
+          <t>AI Chatbot Configuration</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2040,17 +2040,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>ADM-408</t>
+          <t>BO-817</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Final Package Approval &amp; Handoff</t>
+          <t>NPS, CSAT &amp; CES Configuration</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Forecasting</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>BO-1069</t>
+          <t>BO-836</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Platform Health &amp; Observability</t>
+          <t>Design System &amp; Components</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2081,22 +2081,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AI governance and human oversight</t>
+          <t>AI configuration assistant</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ADM-618</t>
+          <t>ADM-408</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Refund Simulator, Risk Analysis &amp; AI Advisor</t>
+          <t>Final Package Approval &amp; Handoff</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>AI governance and human oversight</t>
+          <t>Forecasting</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>BO-1072</t>
+          <t>BO-1069</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Seat Management APIs</t>
+          <t>Platform Health &amp; Observability</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>BO-528</t>
+          <t>ADM-618</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Dynamic Pricing &amp; AI Recommendation</t>
+          <t>Refund Simulator, Risk Analysis &amp; AI Advisor</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2160,12 +2160,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>BO-824</t>
+          <t>BO-1072</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Gamification Command Center</t>
+          <t>Seat Management APIs</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>BO-841</t>
+          <t>BO-528</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Personalization &amp; Localization</t>
+          <t>Dynamic Pricing &amp; AI Recommendation</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>BO-998</t>
+          <t>BO-824</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Lock Timeout &amp; Concurrency</t>
+          <t>Gamification Command Center</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2219,22 +2219,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI governance and human oversight</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>EMP-044</t>
+          <t>BO-841</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Personalization &amp; Localization</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2242,22 +2242,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AI governance and human oversight</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>EMP-045</t>
+          <t>BO-998</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Arabic / RTL</t>
+          <t>Lock Timeout &amp; Concurrency</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2270,17 +2270,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>ADM-097</t>
+          <t>EMP-044</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Rule Priority, Conflict Resolution &amp; Dynamic Pricing Test Console</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2293,17 +2293,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>ADM-169</t>
+          <t>EMP-045</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Buy X Get Y / BOGO Rule Builder</t>
+          <t>Arabic / RTL</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ADM-172</t>
+          <t>ADM-097</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Fixed-Price &amp; “N for X” Offer Builder</t>
+          <t>Rule Priority, Conflict Resolution &amp; Dynamic Pricing Test Console</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>ADM-173</t>
+          <t>ADM-169</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Gift, Free Product &amp; Added-Value Offer Builder</t>
+          <t>Buy X Get Y / BOGO Rule Builder</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ADM-174</t>
+          <t>ADM-172</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Cross-Category Promotion Builder</t>
+          <t>Fixed-Price &amp; “N for X” Offer Builder</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>ADM-199</t>
+          <t>ADM-173</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Eligibility Rule Builder</t>
+          <t>Gift, Free Product &amp; Added-Value Offer Builder</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ADM-249</t>
+          <t>ADM-174</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Unified Approval Inbox &amp; Decision Workspace</t>
+          <t>Cross-Category Promotion Builder</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>ADM-252</t>
+          <t>ADM-199</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>SLA, Escalation &amp; Bottleneck Monitor</t>
+          <t>Eligibility Rule Builder</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ADM-344</t>
+          <t>ADM-249</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Digital Signature Management</t>
+          <t>Unified Approval Inbox &amp; Decision Workspace</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>BO-031</t>
+          <t>ADM-252</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Asset Register</t>
+          <t>SLA, Escalation &amp; Bottleneck Monitor</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>BO-110</t>
+          <t>ADM-344</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Recipe &amp; BOM Management</t>
+          <t>Digital Signature Management</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>BO-113</t>
+          <t>ADM-612</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Central Kitchen &amp; Commissary Management</t>
+          <t>Refund Allocation &amp; Original Tender Manager</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>BO-1133</t>
+          <t>BO-031</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Wallet Usage &amp; Channel Command Center</t>
+          <t>Asset Register</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>BO-138</t>
+          <t>BO-110</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Production Execution &amp; Batch Management</t>
+          <t>Recipe &amp; BOM Management</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>BO-365</t>
+          <t>BO-113</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>My Approval Inbox</t>
+          <t>Central Kitchen &amp; Commissary Management</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BO-432</t>
+          <t>BO-1133</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Gameplay Authorization</t>
+          <t>Wallet Usage &amp; Channel Command Center</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>BO-444</t>
+          <t>BO-138</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Redemption Operations Dashboard</t>
+          <t>Production Execution &amp; Batch Management</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>BO-458</t>
+          <t>BO-365</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Expiry Monitoring &amp; Upcoming Expiration</t>
+          <t>My Approval Inbox</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>BO-477</t>
+          <t>BO-432</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Reader Command &amp; Event Mapping</t>
+          <t>Real-Time Gameplay Authorization</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>BO-483</t>
+          <t>BO-444</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Integration Certification &amp; Test Console</t>
+          <t>Redemption Operations Dashboard</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>BO-484</t>
+          <t>BO-458</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Self-Service Experience Command Center</t>
+          <t>Expiry Monitoring &amp; Upcoming Expiration</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2758,12 +2758,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>BO-587</t>
+          <t>BO-477</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Inventory &amp; Equipment Performance Analytics</t>
+          <t>Reader Command &amp; Event Mapping</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>BO-674</t>
+          <t>BO-483</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Accreditation Communications Command Center</t>
+          <t>Integration Certification &amp; Test Console</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>BO-677</t>
+          <t>BO-484</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Communication Template Library</t>
+          <t>Self-Service Experience Command Center</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BO-679</t>
+          <t>BO-587</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Manual &amp; Bulk Communication Center</t>
+          <t>Inventory &amp; Equipment Performance Analytics</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>BO-681</t>
+          <t>BO-674</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Import Validation &amp; Processing Monitor</t>
+          <t>Accreditation Communications Command Center</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>BO-728</t>
+          <t>BO-677</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Outlet Management</t>
+          <t>Communication Template Library</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>BO-729</t>
+          <t>BO-679</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Create / Edit Outlet</t>
+          <t>Manual &amp; Bulk Communication Center</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>BO-812</t>
+          <t>BO-681</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Service Recovery</t>
+          <t>Import Validation &amp; Processing Monitor</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>BO-822</t>
+          <t>BO-728</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Service Recovery Automation</t>
+          <t>Outlet Management</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>BO-838</t>
+          <t>BO-729</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Content, Media &amp; Forms</t>
+          <t>Create / Edit Outlet</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>BO-942</t>
+          <t>BO-812</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Mobile Operations Control &amp; Offline Sync</t>
+          <t>Service Recovery</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3006,17 +3006,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ADM-379</t>
+          <t>BO-822</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
+          <t>Service Recovery Automation</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3029,17 +3029,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>ADM-409</t>
+          <t>BO-838</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Purchase / Trial Journey Selection</t>
+          <t>Content, Media &amp; Forms</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3052,17 +3052,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ACC-001</t>
+          <t>BO-917</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Landing / Programme Overview</t>
+          <t>Event Staff &amp; Personnel Allocation</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3075,17 +3075,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>SGN-001</t>
+          <t>BO-942</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Welcome &amp; Start Your TICVAI Journey</t>
+          <t>Mobile Operations Control &amp; Offline Sync</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3098,17 +3098,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>SGN-018</t>
+          <t>ADM-379</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Purchase / Trial Journey Selection</t>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3121,17 +3121,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>SGN-019</t>
+          <t>ADM-409</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Contract &amp; Billing Cycle Selection</t>
+          <t>Purchase / Trial Journey Selection</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3144,20 +3144,112 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>ACC-001</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Landing / Programme Overview</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>SGN-001</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Welcome &amp; Start Your TICVAI Journey</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>SGN-018</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Purchase / Trial Journey Selection</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>SGN-019</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Contract &amp; Billing Cycle Selection</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>SGN-024</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Subscription Confirmation &amp; Commercial Activation</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
